--- a/Test Results/Excel/Automation_Test_Report.xlsx
+++ b/Test Results/Excel/Automation_Test_Report.xlsx
@@ -468,7 +468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F2" t="str">
-        <v>0.059s</v>
+        <v>0.137s</v>
       </c>
       <c r="G2" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -508,7 +508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F3" t="str">
-        <v>0.153s</v>
+        <v>0.143s</v>
       </c>
       <c r="G3" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -548,7 +548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F4" t="str">
-        <v>0.108s</v>
+        <v>0.117s</v>
       </c>
       <c r="G4" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -588,7 +588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F5" t="str">
-        <v>0.140s</v>
+        <v>0.057s</v>
       </c>
       <c r="G5" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -628,7 +628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F6" t="str">
-        <v>0.096s</v>
+        <v>0.118s</v>
       </c>
       <c r="G6" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -668,7 +668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F7" t="str">
-        <v>0.069s</v>
+        <v>0.064s</v>
       </c>
       <c r="G7" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -708,7 +708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F8" t="str">
-        <v>0.068s</v>
+        <v>0.070s</v>
       </c>
       <c r="G8" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -748,7 +748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F9" t="str">
-        <v>0.057s</v>
+        <v>0.069s</v>
       </c>
       <c r="G9" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -788,7 +788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F10" t="str">
-        <v>0.094s</v>
+        <v>0.137s</v>
       </c>
       <c r="G10" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -828,7 +828,7 @@
         <v>FAILED</v>
       </c>
       <c r="F11" t="str">
-        <v>0.121s</v>
+        <v>0.157s</v>
       </c>
       <c r="G11" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -868,7 +868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F12" t="str">
-        <v>0.143s</v>
+        <v>0.093s</v>
       </c>
       <c r="G12" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -908,7 +908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F13" t="str">
-        <v>0.056s</v>
+        <v>0.044s</v>
       </c>
       <c r="G13" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -948,7 +948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F14" t="str">
-        <v>0.155s</v>
+        <v>0.059s</v>
       </c>
       <c r="G14" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -988,7 +988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F15" t="str">
-        <v>0.043s</v>
+        <v>0.065s</v>
       </c>
       <c r="G15" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1028,7 +1028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F16" t="str">
-        <v>0.060s</v>
+        <v>0.097s</v>
       </c>
       <c r="G16" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1068,7 +1068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F17" t="str">
-        <v>0.113s</v>
+        <v>0.076s</v>
       </c>
       <c r="G17" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1108,7 +1108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F18" t="str">
-        <v>0.060s</v>
+        <v>0.087s</v>
       </c>
       <c r="G18" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1148,7 +1148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F19" t="str">
-        <v>0.057s</v>
+        <v>0.146s</v>
       </c>
       <c r="G19" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1188,7 +1188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F20" t="str">
-        <v>0.141s</v>
+        <v>0.100s</v>
       </c>
       <c r="G20" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1228,7 +1228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F21" t="str">
-        <v>0.119s</v>
+        <v>0.043s</v>
       </c>
       <c r="G21" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1268,7 +1268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F22" t="str">
-        <v>0.109s</v>
+        <v>0.148s</v>
       </c>
       <c r="G22" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1308,7 +1308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F23" t="str">
-        <v>0.073s</v>
+        <v>0.095s</v>
       </c>
       <c r="G23" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1348,7 +1348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F24" t="str">
-        <v>0.083s</v>
+        <v>0.082s</v>
       </c>
       <c r="G24" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1388,7 +1388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F25" t="str">
-        <v>0.047s</v>
+        <v>0.055s</v>
       </c>
       <c r="G25" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1428,7 +1428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F26" t="str">
-        <v>0.047s</v>
+        <v>0.149s</v>
       </c>
       <c r="G26" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1468,7 +1468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F27" t="str">
-        <v>0.095s</v>
+        <v>0.044s</v>
       </c>
       <c r="G27" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1548,7 +1548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F29" t="str">
-        <v>0.044s</v>
+        <v>0.073s</v>
       </c>
       <c r="G29" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1588,7 +1588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F30" t="str">
-        <v>0.160s</v>
+        <v>0.106s</v>
       </c>
       <c r="G30" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1628,7 +1628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F31" t="str">
-        <v>0.090s</v>
+        <v>0.066s</v>
       </c>
       <c r="G31" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1668,7 +1668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F32" t="str">
-        <v>0.051s</v>
+        <v>0.151s</v>
       </c>
       <c r="G32" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1708,7 +1708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F33" t="str">
-        <v>0.063s</v>
+        <v>0.088s</v>
       </c>
       <c r="G33" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1748,7 +1748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F34" t="str">
-        <v>0.081s</v>
+        <v>0.125s</v>
       </c>
       <c r="G34" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1788,7 +1788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F35" t="str">
-        <v>0.141s</v>
+        <v>0.067s</v>
       </c>
       <c r="G35" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1828,7 +1828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F36" t="str">
-        <v>0.077s</v>
+        <v>0.102s</v>
       </c>
       <c r="G36" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1868,7 +1868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F37" t="str">
-        <v>0.066s</v>
+        <v>0.153s</v>
       </c>
       <c r="G37" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1908,7 +1908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F38" t="str">
-        <v>0.133s</v>
+        <v>0.071s</v>
       </c>
       <c r="G38" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1948,7 +1948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F39" t="str">
-        <v>0.153s</v>
+        <v>0.134s</v>
       </c>
       <c r="G39" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -1988,7 +1988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F40" t="str">
-        <v>0.061s</v>
+        <v>0.084s</v>
       </c>
       <c r="G40" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2028,7 +2028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F41" t="str">
-        <v>0.120s</v>
+        <v>0.099s</v>
       </c>
       <c r="G41" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2068,7 +2068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F42" t="str">
-        <v>0.095s</v>
+        <v>0.055s</v>
       </c>
       <c r="G42" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2108,7 +2108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F43" t="str">
-        <v>0.077s</v>
+        <v>0.075s</v>
       </c>
       <c r="G43" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2148,7 +2148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F44" t="str">
-        <v>0.139s</v>
+        <v>0.157s</v>
       </c>
       <c r="G44" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2188,7 +2188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F45" t="str">
-        <v>0.146s</v>
+        <v>0.057s</v>
       </c>
       <c r="G45" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2228,7 +2228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F46" t="str">
-        <v>0.098s</v>
+        <v>0.145s</v>
       </c>
       <c r="G46" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2268,7 +2268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F47" t="str">
-        <v>0.089s</v>
+        <v>0.149s</v>
       </c>
       <c r="G47" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2308,7 +2308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F48" t="str">
-        <v>0.089s</v>
+        <v>0.103s</v>
       </c>
       <c r="G48" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2348,7 +2348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F49" t="str">
-        <v>0.077s</v>
+        <v>0.082s</v>
       </c>
       <c r="G49" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2388,7 +2388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F50" t="str">
-        <v>0.138s</v>
+        <v>0.117s</v>
       </c>
       <c r="G50" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2428,7 +2428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F51" t="str">
-        <v>0.062s</v>
+        <v>0.131s</v>
       </c>
       <c r="G51" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2468,7 +2468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F52" t="str">
-        <v>0.105s</v>
+        <v>0.092s</v>
       </c>
       <c r="G52" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2508,7 +2508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F53" t="str">
-        <v>0.078s</v>
+        <v>0.139s</v>
       </c>
       <c r="G53" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2548,7 +2548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F54" t="str">
-        <v>0.061s</v>
+        <v>0.057s</v>
       </c>
       <c r="G54" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2588,7 +2588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F55" t="str">
-        <v>0.139s</v>
+        <v>0.152s</v>
       </c>
       <c r="G55" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2628,7 +2628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F56" t="str">
-        <v>0.060s</v>
+        <v>0.062s</v>
       </c>
       <c r="G56" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2668,7 +2668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F57" t="str">
-        <v>0.066s</v>
+        <v>0.142s</v>
       </c>
       <c r="G57" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2708,7 +2708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F58" t="str">
-        <v>0.092s</v>
+        <v>0.130s</v>
       </c>
       <c r="G58" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2748,7 +2748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F59" t="str">
-        <v>0.117s</v>
+        <v>0.041s</v>
       </c>
       <c r="G59" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2788,7 +2788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F60" t="str">
-        <v>0.157s</v>
+        <v>0.129s</v>
       </c>
       <c r="G60" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2828,7 +2828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F61" t="str">
-        <v>0.130s</v>
+        <v>0.133s</v>
       </c>
       <c r="G61" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2868,7 +2868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F62" t="str">
-        <v>0.115s</v>
+        <v>0.063s</v>
       </c>
       <c r="G62" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2908,7 +2908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F63" t="str">
-        <v>0.118s</v>
+        <v>0.122s</v>
       </c>
       <c r="G63" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2948,7 +2948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F64" t="str">
-        <v>0.089s</v>
+        <v>0.094s</v>
       </c>
       <c r="G64" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -2988,7 +2988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F65" t="str">
-        <v>0.063s</v>
+        <v>0.147s</v>
       </c>
       <c r="G65" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3028,7 +3028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F66" t="str">
-        <v>0.134s</v>
+        <v>0.046s</v>
       </c>
       <c r="G66" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3068,7 +3068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F67" t="str">
-        <v>0.045s</v>
+        <v>0.062s</v>
       </c>
       <c r="G67" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3108,7 +3108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F68" t="str">
-        <v>0.052s</v>
+        <v>0.155s</v>
       </c>
       <c r="G68" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3148,7 +3148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F69" t="str">
-        <v>0.047s</v>
+        <v>0.065s</v>
       </c>
       <c r="G69" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3188,7 +3188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F70" t="str">
-        <v>0.138s</v>
+        <v>0.083s</v>
       </c>
       <c r="G70" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3228,7 +3228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F71" t="str">
-        <v>0.062s</v>
+        <v>0.121s</v>
       </c>
       <c r="G71" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3268,7 +3268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F72" t="str">
-        <v>0.072s</v>
+        <v>0.073s</v>
       </c>
       <c r="G72" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3308,7 +3308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F73" t="str">
-        <v>0.116s</v>
+        <v>0.049s</v>
       </c>
       <c r="G73" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3348,7 +3348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F74" t="str">
-        <v>0.071s</v>
+        <v>0.098s</v>
       </c>
       <c r="G74" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3388,7 +3388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F75" t="str">
-        <v>0.051s</v>
+        <v>0.132s</v>
       </c>
       <c r="G75" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3428,7 +3428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F76" t="str">
-        <v>0.080s</v>
+        <v>0.139s</v>
       </c>
       <c r="G76" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3468,7 +3468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F77" t="str">
-        <v>0.114s</v>
+        <v>0.112s</v>
       </c>
       <c r="G77" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3508,7 +3508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F78" t="str">
-        <v>0.121s</v>
+        <v>0.076s</v>
       </c>
       <c r="G78" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3548,7 +3548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F79" t="str">
-        <v>0.072s</v>
+        <v>0.155s</v>
       </c>
       <c r="G79" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3588,7 +3588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F80" t="str">
-        <v>0.077s</v>
+        <v>0.083s</v>
       </c>
       <c r="G80" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3628,7 +3628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F81" t="str">
-        <v>0.155s</v>
+        <v>0.078s</v>
       </c>
       <c r="G81" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3668,7 +3668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F82" t="str">
-        <v>0.108s</v>
+        <v>0.052s</v>
       </c>
       <c r="G82" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3708,7 +3708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F83" t="str">
-        <v>0.124s</v>
+        <v>0.150s</v>
       </c>
       <c r="G83" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3748,7 +3748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F84" t="str">
-        <v>0.047s</v>
+        <v>0.086s</v>
       </c>
       <c r="G84" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3788,7 +3788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F85" t="str">
-        <v>0.121s</v>
+        <v>0.093s</v>
       </c>
       <c r="G85" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3828,7 +3828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F86" t="str">
-        <v>0.051s</v>
+        <v>0.147s</v>
       </c>
       <c r="G86" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3868,7 +3868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F87" t="str">
-        <v>0.055s</v>
+        <v>0.057s</v>
       </c>
       <c r="G87" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3908,7 +3908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F88" t="str">
-        <v>0.148s</v>
+        <v>0.055s</v>
       </c>
       <c r="G88" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3948,7 +3948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F89" t="str">
-        <v>0.088s</v>
+        <v>0.055s</v>
       </c>
       <c r="G89" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -3988,7 +3988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F90" t="str">
-        <v>0.138s</v>
+        <v>0.148s</v>
       </c>
       <c r="G90" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4028,7 +4028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F91" t="str">
-        <v>0.156s</v>
+        <v>0.068s</v>
       </c>
       <c r="G91" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4068,7 +4068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F92" t="str">
-        <v>0.127s</v>
+        <v>0.138s</v>
       </c>
       <c r="G92" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4108,7 +4108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F93" t="str">
-        <v>0.139s</v>
+        <v>0.071s</v>
       </c>
       <c r="G93" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4148,7 +4148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F94" t="str">
-        <v>0.160s</v>
+        <v>0.048s</v>
       </c>
       <c r="G94" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4188,7 +4188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F95" t="str">
-        <v>0.043s</v>
+        <v>0.142s</v>
       </c>
       <c r="G95" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4228,7 +4228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F96" t="str">
-        <v>0.145s</v>
+        <v>0.087s</v>
       </c>
       <c r="G96" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4268,7 +4268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F97" t="str">
-        <v>0.091s</v>
+        <v>0.058s</v>
       </c>
       <c r="G97" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4308,7 +4308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F98" t="str">
-        <v>0.071s</v>
+        <v>0.104s</v>
       </c>
       <c r="G98" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4348,7 +4348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F99" t="str">
-        <v>0.077s</v>
+        <v>0.089s</v>
       </c>
       <c r="G99" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4388,7 +4388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F100" t="str">
-        <v>0.144s</v>
+        <v>0.103s</v>
       </c>
       <c r="G100" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4428,7 +4428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F101" t="str">
-        <v>0.065s</v>
+        <v>0.139s</v>
       </c>
       <c r="G101" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4468,7 +4468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F102" t="str">
-        <v>0.080s</v>
+        <v>0.081s</v>
       </c>
       <c r="G102" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4508,7 +4508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F103" t="str">
-        <v>0.148s</v>
+        <v>0.054s</v>
       </c>
       <c r="G103" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4548,7 +4548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F104" t="str">
-        <v>0.114s</v>
+        <v>0.120s</v>
       </c>
       <c r="G104" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4588,7 +4588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F105" t="str">
-        <v>0.155s</v>
+        <v>0.071s</v>
       </c>
       <c r="G105" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4628,7 +4628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F106" t="str">
-        <v>0.096s</v>
+        <v>0.102s</v>
       </c>
       <c r="G106" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4668,7 +4668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F107" t="str">
-        <v>0.044s</v>
+        <v>0.086s</v>
       </c>
       <c r="G107" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4708,7 +4708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F108" t="str">
-        <v>0.151s</v>
+        <v>0.078s</v>
       </c>
       <c r="G108" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4748,7 +4748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F109" t="str">
-        <v>0.125s</v>
+        <v>0.137s</v>
       </c>
       <c r="G109" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4788,7 +4788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F110" t="str">
-        <v>0.070s</v>
+        <v>0.062s</v>
       </c>
       <c r="G110" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4828,7 +4828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F111" t="str">
-        <v>0.152s</v>
+        <v>0.055s</v>
       </c>
       <c r="G111" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4868,7 +4868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F112" t="str">
-        <v>0.121s</v>
+        <v>0.109s</v>
       </c>
       <c r="G112" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4908,7 +4908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F113" t="str">
-        <v>0.086s</v>
+        <v>0.097s</v>
       </c>
       <c r="G113" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4948,7 +4948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F114" t="str">
-        <v>0.080s</v>
+        <v>0.108s</v>
       </c>
       <c r="G114" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -4988,7 +4988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F115" t="str">
-        <v>0.072s</v>
+        <v>0.111s</v>
       </c>
       <c r="G115" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5028,7 +5028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F116" t="str">
-        <v>0.086s</v>
+        <v>0.150s</v>
       </c>
       <c r="G116" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5068,7 +5068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F117" t="str">
-        <v>0.143s</v>
+        <v>0.136s</v>
       </c>
       <c r="G117" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5108,7 +5108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F118" t="str">
-        <v>0.155s</v>
+        <v>0.149s</v>
       </c>
       <c r="G118" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5148,7 +5148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F119" t="str">
-        <v>0.108s</v>
+        <v>0.076s</v>
       </c>
       <c r="G119" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5188,7 +5188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F120" t="str">
-        <v>0.115s</v>
+        <v>0.065s</v>
       </c>
       <c r="G120" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5228,7 +5228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F121" t="str">
-        <v>0.044s</v>
+        <v>0.139s</v>
       </c>
       <c r="G121" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5268,7 +5268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F122" t="str">
-        <v>0.114s</v>
+        <v>0.147s</v>
       </c>
       <c r="G122" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5308,7 +5308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F123" t="str">
-        <v>0.093s</v>
+        <v>0.121s</v>
       </c>
       <c r="G123" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5348,7 +5348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F124" t="str">
-        <v>0.130s</v>
+        <v>0.058s</v>
       </c>
       <c r="G124" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5388,7 +5388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F125" t="str">
-        <v>0.113s</v>
+        <v>0.069s</v>
       </c>
       <c r="G125" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5428,7 +5428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F126" t="str">
-        <v>0.115s</v>
+        <v>0.040s</v>
       </c>
       <c r="G126" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5468,7 +5468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F127" t="str">
-        <v>0.080s</v>
+        <v>0.138s</v>
       </c>
       <c r="G127" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5508,7 +5508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F128" t="str">
-        <v>0.136s</v>
+        <v>0.132s</v>
       </c>
       <c r="G128" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5548,7 +5548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F129" t="str">
-        <v>0.157s</v>
+        <v>0.092s</v>
       </c>
       <c r="G129" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5588,7 +5588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F130" t="str">
-        <v>0.072s</v>
+        <v>0.135s</v>
       </c>
       <c r="G130" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5628,7 +5628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F131" t="str">
-        <v>0.121s</v>
+        <v>0.090s</v>
       </c>
       <c r="G131" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5708,7 +5708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F133" t="str">
-        <v>0.149s</v>
+        <v>0.082s</v>
       </c>
       <c r="G133" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5748,7 +5748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F134" t="str">
-        <v>0.093s</v>
+        <v>0.114s</v>
       </c>
       <c r="G134" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5788,7 +5788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F135" t="str">
-        <v>0.043s</v>
+        <v>0.065s</v>
       </c>
       <c r="G135" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5828,7 +5828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F136" t="str">
-        <v>0.077s</v>
+        <v>0.055s</v>
       </c>
       <c r="G136" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5868,7 +5868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F137" t="str">
-        <v>0.056s</v>
+        <v>0.100s</v>
       </c>
       <c r="G137" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5908,7 +5908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F138" t="str">
-        <v>0.050s</v>
+        <v>0.127s</v>
       </c>
       <c r="G138" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5948,7 +5948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F139" t="str">
-        <v>0.153s</v>
+        <v>0.139s</v>
       </c>
       <c r="G139" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -5988,7 +5988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F140" t="str">
-        <v>0.054s</v>
+        <v>0.052s</v>
       </c>
       <c r="G140" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6028,7 +6028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F141" t="str">
-        <v>0.153s</v>
+        <v>0.148s</v>
       </c>
       <c r="G141" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6068,7 +6068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F142" t="str">
-        <v>0.097s</v>
+        <v>0.063s</v>
       </c>
       <c r="G142" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6108,7 +6108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F143" t="str">
-        <v>0.117s</v>
+        <v>0.157s</v>
       </c>
       <c r="G143" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6148,7 +6148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F144" t="str">
-        <v>0.099s</v>
+        <v>0.123s</v>
       </c>
       <c r="G144" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6188,7 +6188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F145" t="str">
-        <v>0.085s</v>
+        <v>0.126s</v>
       </c>
       <c r="G145" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6228,7 +6228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F146" t="str">
-        <v>0.114s</v>
+        <v>0.089s</v>
       </c>
       <c r="G146" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6268,7 +6268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F147" t="str">
-        <v>0.151s</v>
+        <v>0.123s</v>
       </c>
       <c r="G147" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6308,7 +6308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F148" t="str">
-        <v>0.067s</v>
+        <v>0.058s</v>
       </c>
       <c r="G148" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6348,7 +6348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F149" t="str">
-        <v>0.066s</v>
+        <v>0.109s</v>
       </c>
       <c r="G149" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6388,7 +6388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F150" t="str">
-        <v>0.111s</v>
+        <v>0.152s</v>
       </c>
       <c r="G150" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6428,7 +6428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F151" t="str">
-        <v>0.133s</v>
+        <v>0.130s</v>
       </c>
       <c r="G151" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6468,7 +6468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F152" t="str">
-        <v>0.093s</v>
+        <v>0.142s</v>
       </c>
       <c r="G152" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6508,7 +6508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F153" t="str">
-        <v>0.101s</v>
+        <v>0.102s</v>
       </c>
       <c r="G153" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6548,7 +6548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F154" t="str">
-        <v>0.105s</v>
+        <v>0.159s</v>
       </c>
       <c r="G154" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6588,7 +6588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F155" t="str">
-        <v>0.048s</v>
+        <v>0.044s</v>
       </c>
       <c r="G155" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6628,7 +6628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F156" t="str">
-        <v>0.125s</v>
+        <v>0.108s</v>
       </c>
       <c r="G156" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6668,7 +6668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F157" t="str">
-        <v>0.043s</v>
+        <v>0.109s</v>
       </c>
       <c r="G157" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6708,7 +6708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F158" t="str">
-        <v>0.138s</v>
+        <v>0.076s</v>
       </c>
       <c r="G158" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6748,7 +6748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F159" t="str">
-        <v>0.103s</v>
+        <v>0.134s</v>
       </c>
       <c r="G159" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6788,7 +6788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F160" t="str">
-        <v>0.132s</v>
+        <v>0.067s</v>
       </c>
       <c r="G160" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6828,7 +6828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F161" t="str">
-        <v>0.148s</v>
+        <v>0.113s</v>
       </c>
       <c r="G161" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6868,7 +6868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F162" t="str">
-        <v>0.113s</v>
+        <v>0.099s</v>
       </c>
       <c r="G162" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6908,7 +6908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F163" t="str">
-        <v>0.104s</v>
+        <v>0.119s</v>
       </c>
       <c r="G163" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6948,7 +6948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F164" t="str">
-        <v>0.124s</v>
+        <v>0.053s</v>
       </c>
       <c r="G164" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -6988,7 +6988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F165" t="str">
-        <v>0.066s</v>
+        <v>0.103s</v>
       </c>
       <c r="G165" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7028,7 +7028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F166" t="str">
-        <v>0.130s</v>
+        <v>0.085s</v>
       </c>
       <c r="G166" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7068,7 +7068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F167" t="str">
-        <v>0.051s</v>
+        <v>0.129s</v>
       </c>
       <c r="G167" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7108,7 +7108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F168" t="str">
-        <v>0.126s</v>
+        <v>0.082s</v>
       </c>
       <c r="G168" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7148,7 +7148,7 @@
         <v>FAILED</v>
       </c>
       <c r="F169" t="str">
-        <v>0.155s</v>
+        <v>0.076s</v>
       </c>
       <c r="G169" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7188,7 +7188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F170" t="str">
-        <v>0.066s</v>
+        <v>0.048s</v>
       </c>
       <c r="G170" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7228,7 +7228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F171" t="str">
-        <v>0.134s</v>
+        <v>0.058s</v>
       </c>
       <c r="G171" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7268,7 +7268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F172" t="str">
-        <v>0.098s</v>
+        <v>0.124s</v>
       </c>
       <c r="G172" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7308,7 +7308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F173" t="str">
-        <v>0.081s</v>
+        <v>0.152s</v>
       </c>
       <c r="G173" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7348,7 +7348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F174" t="str">
-        <v>0.137s</v>
+        <v>0.128s</v>
       </c>
       <c r="G174" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7388,7 +7388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F175" t="str">
-        <v>0.146s</v>
+        <v>0.125s</v>
       </c>
       <c r="G175" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7428,7 +7428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F176" t="str">
-        <v>0.117s</v>
+        <v>0.146s</v>
       </c>
       <c r="G176" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7468,7 +7468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F177" t="str">
-        <v>0.117s</v>
+        <v>0.125s</v>
       </c>
       <c r="G177" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7508,7 +7508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F178" t="str">
-        <v>0.056s</v>
+        <v>0.122s</v>
       </c>
       <c r="G178" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7548,7 +7548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F179" t="str">
-        <v>0.097s</v>
+        <v>0.159s</v>
       </c>
       <c r="G179" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7588,7 +7588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F180" t="str">
-        <v>0.117s</v>
+        <v>0.053s</v>
       </c>
       <c r="G180" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7628,7 +7628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F181" t="str">
-        <v>0.042s</v>
+        <v>0.113s</v>
       </c>
       <c r="G181" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7668,7 +7668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F182" t="str">
-        <v>0.051s</v>
+        <v>0.111s</v>
       </c>
       <c r="G182" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7708,7 +7708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F183" t="str">
-        <v>0.135s</v>
+        <v>0.117s</v>
       </c>
       <c r="G183" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7748,7 +7748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F184" t="str">
-        <v>0.113s</v>
+        <v>0.078s</v>
       </c>
       <c r="G184" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7788,7 +7788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F185" t="str">
-        <v>0.057s</v>
+        <v>0.090s</v>
       </c>
       <c r="G185" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7828,7 +7828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F186" t="str">
-        <v>0.080s</v>
+        <v>0.158s</v>
       </c>
       <c r="G186" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7868,7 +7868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F187" t="str">
-        <v>0.131s</v>
+        <v>0.141s</v>
       </c>
       <c r="G187" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7908,7 +7908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F188" t="str">
-        <v>0.159s</v>
+        <v>0.139s</v>
       </c>
       <c r="G188" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7948,7 +7948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F189" t="str">
-        <v>0.143s</v>
+        <v>0.092s</v>
       </c>
       <c r="G189" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -7988,7 +7988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F190" t="str">
-        <v>0.117s</v>
+        <v>0.044s</v>
       </c>
       <c r="G190" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8028,7 +8028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F191" t="str">
-        <v>0.149s</v>
+        <v>0.135s</v>
       </c>
       <c r="G191" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8068,7 +8068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F192" t="str">
-        <v>0.147s</v>
+        <v>0.064s</v>
       </c>
       <c r="G192" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8108,7 +8108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F193" t="str">
-        <v>0.062s</v>
+        <v>0.141s</v>
       </c>
       <c r="G193" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8148,7 +8148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F194" t="str">
-        <v>0.074s</v>
+        <v>0.051s</v>
       </c>
       <c r="G194" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8188,7 +8188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F195" t="str">
-        <v>0.103s</v>
+        <v>0.156s</v>
       </c>
       <c r="G195" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8228,7 +8228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F196" t="str">
-        <v>0.147s</v>
+        <v>0.158s</v>
       </c>
       <c r="G196" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8268,7 +8268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F197" t="str">
-        <v>0.136s</v>
+        <v>0.143s</v>
       </c>
       <c r="G197" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8308,7 +8308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F198" t="str">
-        <v>0.098s</v>
+        <v>0.120s</v>
       </c>
       <c r="G198" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8348,7 +8348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F199" t="str">
-        <v>0.085s</v>
+        <v>0.048s</v>
       </c>
       <c r="G199" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8388,7 +8388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F200" t="str">
-        <v>0.123s</v>
+        <v>0.102s</v>
       </c>
       <c r="G200" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8428,7 +8428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F201" t="str">
-        <v>0.122s</v>
+        <v>0.106s</v>
       </c>
       <c r="G201" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8468,7 +8468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F202" t="str">
-        <v>0.058s</v>
+        <v>0.077s</v>
       </c>
       <c r="G202" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8508,7 +8508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F203" t="str">
-        <v>0.065s</v>
+        <v>0.107s</v>
       </c>
       <c r="G203" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8548,7 +8548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F204" t="str">
-        <v>0.066s</v>
+        <v>0.125s</v>
       </c>
       <c r="G204" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8588,7 +8588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F205" t="str">
-        <v>0.055s</v>
+        <v>0.126s</v>
       </c>
       <c r="G205" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8628,7 +8628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F206" t="str">
-        <v>0.150s</v>
+        <v>0.078s</v>
       </c>
       <c r="G206" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8668,7 +8668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F207" t="str">
-        <v>0.042s</v>
+        <v>0.155s</v>
       </c>
       <c r="G207" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8708,7 +8708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F208" t="str">
-        <v>0.112s</v>
+        <v>0.081s</v>
       </c>
       <c r="G208" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8748,7 +8748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F209" t="str">
-        <v>0.090s</v>
+        <v>0.051s</v>
       </c>
       <c r="G209" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8788,7 +8788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F210" t="str">
-        <v>0.158s</v>
+        <v>0.134s</v>
       </c>
       <c r="G210" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8828,7 +8828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F211" t="str">
-        <v>0.122s</v>
+        <v>0.144s</v>
       </c>
       <c r="G211" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8868,7 +8868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F212" t="str">
-        <v>0.066s</v>
+        <v>0.077s</v>
       </c>
       <c r="G212" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8908,7 +8908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F213" t="str">
-        <v>0.149s</v>
+        <v>0.117s</v>
       </c>
       <c r="G213" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8948,7 +8948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F214" t="str">
-        <v>0.111s</v>
+        <v>0.145s</v>
       </c>
       <c r="G214" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -8988,7 +8988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F215" t="str">
-        <v>0.052s</v>
+        <v>0.108s</v>
       </c>
       <c r="G215" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9028,7 +9028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F216" t="str">
-        <v>0.062s</v>
+        <v>0.086s</v>
       </c>
       <c r="G216" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9068,7 +9068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F217" t="str">
-        <v>0.128s</v>
+        <v>0.065s</v>
       </c>
       <c r="G217" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9108,7 +9108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F218" t="str">
-        <v>0.130s</v>
+        <v>0.149s</v>
       </c>
       <c r="G218" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9148,7 +9148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F219" t="str">
-        <v>0.063s</v>
+        <v>0.082s</v>
       </c>
       <c r="G219" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9188,7 +9188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F220" t="str">
-        <v>0.127s</v>
+        <v>0.088s</v>
       </c>
       <c r="G220" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9228,7 +9228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F221" t="str">
-        <v>0.102s</v>
+        <v>0.050s</v>
       </c>
       <c r="G221" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9268,7 +9268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F222" t="str">
-        <v>0.113s</v>
+        <v>0.089s</v>
       </c>
       <c r="G222" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9308,7 +9308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F223" t="str">
-        <v>0.132s</v>
+        <v>0.109s</v>
       </c>
       <c r="G223" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9348,7 +9348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F224" t="str">
-        <v>0.135s</v>
+        <v>0.068s</v>
       </c>
       <c r="G224" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9388,7 +9388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F225" t="str">
-        <v>0.081s</v>
+        <v>0.117s</v>
       </c>
       <c r="G225" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9428,7 +9428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F226" t="str">
-        <v>0.124s</v>
+        <v>0.112s</v>
       </c>
       <c r="G226" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9468,7 +9468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F227" t="str">
-        <v>0.071s</v>
+        <v>0.074s</v>
       </c>
       <c r="G227" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9508,7 +9508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F228" t="str">
-        <v>0.063s</v>
+        <v>0.151s</v>
       </c>
       <c r="G228" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9548,7 +9548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F229" t="str">
-        <v>0.133s</v>
+        <v>0.100s</v>
       </c>
       <c r="G229" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9588,7 +9588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F230" t="str">
-        <v>0.123s</v>
+        <v>0.047s</v>
       </c>
       <c r="G230" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9628,7 +9628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F231" t="str">
-        <v>0.063s</v>
+        <v>0.067s</v>
       </c>
       <c r="G231" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9668,7 +9668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F232" t="str">
-        <v>0.051s</v>
+        <v>0.107s</v>
       </c>
       <c r="G232" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9708,7 +9708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F233" t="str">
-        <v>0.070s</v>
+        <v>0.071s</v>
       </c>
       <c r="G233" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9748,7 +9748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F234" t="str">
-        <v>0.079s</v>
+        <v>0.101s</v>
       </c>
       <c r="G234" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9788,7 +9788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F235" t="str">
-        <v>0.148s</v>
+        <v>0.137s</v>
       </c>
       <c r="G235" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9828,7 +9828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F236" t="str">
-        <v>0.140s</v>
+        <v>0.079s</v>
       </c>
       <c r="G236" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9868,7 +9868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F237" t="str">
-        <v>0.104s</v>
+        <v>0.096s</v>
       </c>
       <c r="G237" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9908,7 +9908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F238" t="str">
-        <v>0.145s</v>
+        <v>0.135s</v>
       </c>
       <c r="G238" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9948,7 +9948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F239" t="str">
-        <v>0.106s</v>
+        <v>0.100s</v>
       </c>
       <c r="G239" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -9988,7 +9988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F240" t="str">
-        <v>0.126s</v>
+        <v>0.146s</v>
       </c>
       <c r="G240" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10028,7 +10028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F241" t="str">
-        <v>0.110s</v>
+        <v>0.042s</v>
       </c>
       <c r="G241" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10068,7 +10068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F242" t="str">
-        <v>0.067s</v>
+        <v>0.063s</v>
       </c>
       <c r="G242" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10108,7 +10108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F243" t="str">
-        <v>0.054s</v>
+        <v>0.152s</v>
       </c>
       <c r="G243" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10148,7 +10148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F244" t="str">
-        <v>0.058s</v>
+        <v>0.147s</v>
       </c>
       <c r="G244" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10188,7 +10188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F245" t="str">
-        <v>0.094s</v>
+        <v>0.040s</v>
       </c>
       <c r="G245" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10228,7 +10228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F246" t="str">
-        <v>0.110s</v>
+        <v>0.081s</v>
       </c>
       <c r="G246" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10268,7 +10268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F247" t="str">
-        <v>0.124s</v>
+        <v>0.092s</v>
       </c>
       <c r="G247" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10308,7 +10308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F248" t="str">
-        <v>0.151s</v>
+        <v>0.143s</v>
       </c>
       <c r="G248" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10348,7 +10348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F249" t="str">
-        <v>0.118s</v>
+        <v>0.064s</v>
       </c>
       <c r="G249" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10388,7 +10388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F250" t="str">
-        <v>0.044s</v>
+        <v>0.075s</v>
       </c>
       <c r="G250" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10428,7 +10428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F251" t="str">
-        <v>0.041s</v>
+        <v>0.138s</v>
       </c>
       <c r="G251" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10468,7 +10468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F252" t="str">
-        <v>0.143s</v>
+        <v>0.053s</v>
       </c>
       <c r="G252" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10508,7 +10508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F253" t="str">
-        <v>0.070s</v>
+        <v>0.072s</v>
       </c>
       <c r="G253" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10548,7 +10548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F254" t="str">
-        <v>0.114s</v>
+        <v>0.137s</v>
       </c>
       <c r="G254" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10588,7 +10588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F255" t="str">
-        <v>0.049s</v>
+        <v>0.071s</v>
       </c>
       <c r="G255" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10628,7 +10628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F256" t="str">
-        <v>0.108s</v>
+        <v>0.148s</v>
       </c>
       <c r="G256" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10668,7 +10668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F257" t="str">
-        <v>0.155s</v>
+        <v>0.147s</v>
       </c>
       <c r="G257" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10708,7 +10708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F258" t="str">
-        <v>0.081s</v>
+        <v>0.103s</v>
       </c>
       <c r="G258" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10748,7 +10748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F259" t="str">
-        <v>0.123s</v>
+        <v>0.096s</v>
       </c>
       <c r="G259" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10788,7 +10788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F260" t="str">
-        <v>0.097s</v>
+        <v>0.057s</v>
       </c>
       <c r="G260" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10868,7 +10868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F262" t="str">
-        <v>0.049s</v>
+        <v>0.051s</v>
       </c>
       <c r="G262" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10908,7 +10908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F263" t="str">
-        <v>0.072s</v>
+        <v>0.150s</v>
       </c>
       <c r="G263" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10948,7 +10948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F264" t="str">
-        <v>0.086s</v>
+        <v>0.041s</v>
       </c>
       <c r="G264" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -10988,7 +10988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F265" t="str">
-        <v>0.111s</v>
+        <v>0.045s</v>
       </c>
       <c r="G265" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11028,7 +11028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F266" t="str">
-        <v>0.075s</v>
+        <v>0.125s</v>
       </c>
       <c r="G266" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11068,7 +11068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F267" t="str">
-        <v>0.080s</v>
+        <v>0.148s</v>
       </c>
       <c r="G267" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11108,7 +11108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F268" t="str">
-        <v>0.076s</v>
+        <v>0.055s</v>
       </c>
       <c r="G268" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11148,7 +11148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F269" t="str">
-        <v>0.070s</v>
+        <v>0.079s</v>
       </c>
       <c r="G269" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11188,7 +11188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F270" t="str">
-        <v>0.049s</v>
+        <v>0.044s</v>
       </c>
       <c r="G270" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11228,7 +11228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F271" t="str">
-        <v>0.158s</v>
+        <v>0.057s</v>
       </c>
       <c r="G271" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11268,7 +11268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F272" t="str">
-        <v>0.067s</v>
+        <v>0.096s</v>
       </c>
       <c r="G272" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11308,7 +11308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F273" t="str">
-        <v>0.059s</v>
+        <v>0.040s</v>
       </c>
       <c r="G273" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11388,7 +11388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F275" t="str">
-        <v>0.107s</v>
+        <v>0.122s</v>
       </c>
       <c r="G275" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11428,7 +11428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F276" t="str">
-        <v>0.107s</v>
+        <v>0.129s</v>
       </c>
       <c r="G276" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11468,7 +11468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F277" t="str">
-        <v>0.110s</v>
+        <v>0.067s</v>
       </c>
       <c r="G277" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11508,7 +11508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F278" t="str">
-        <v>0.075s</v>
+        <v>0.132s</v>
       </c>
       <c r="G278" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11548,7 +11548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F279" t="str">
-        <v>0.149s</v>
+        <v>0.101s</v>
       </c>
       <c r="G279" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11588,7 +11588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F280" t="str">
-        <v>0.065s</v>
+        <v>0.049s</v>
       </c>
       <c r="G280" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11628,7 +11628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F281" t="str">
-        <v>0.076s</v>
+        <v>0.091s</v>
       </c>
       <c r="G281" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11668,7 +11668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F282" t="str">
-        <v>0.063s</v>
+        <v>0.156s</v>
       </c>
       <c r="G282" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11708,7 +11708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F283" t="str">
-        <v>0.099s</v>
+        <v>0.108s</v>
       </c>
       <c r="G283" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11748,7 +11748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F284" t="str">
-        <v>0.049s</v>
+        <v>0.107s</v>
       </c>
       <c r="G284" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11788,7 +11788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F285" t="str">
-        <v>0.073s</v>
+        <v>0.095s</v>
       </c>
       <c r="G285" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11828,7 +11828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F286" t="str">
-        <v>0.095s</v>
+        <v>0.046s</v>
       </c>
       <c r="G286" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11868,7 +11868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F287" t="str">
-        <v>0.133s</v>
+        <v>0.094s</v>
       </c>
       <c r="G287" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11908,7 +11908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F288" t="str">
-        <v>0.087s</v>
+        <v>0.150s</v>
       </c>
       <c r="G288" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11948,7 +11948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F289" t="str">
-        <v>0.110s</v>
+        <v>0.154s</v>
       </c>
       <c r="G289" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -11988,7 +11988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F290" t="str">
-        <v>0.111s</v>
+        <v>0.084s</v>
       </c>
       <c r="G290" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12028,7 +12028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F291" t="str">
-        <v>0.110s</v>
+        <v>0.070s</v>
       </c>
       <c r="G291" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12068,7 +12068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F292" t="str">
-        <v>0.073s</v>
+        <v>0.070s</v>
       </c>
       <c r="G292" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12108,7 +12108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F293" t="str">
-        <v>0.044s</v>
+        <v>0.051s</v>
       </c>
       <c r="G293" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12148,7 +12148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F294" t="str">
-        <v>0.060s</v>
+        <v>0.132s</v>
       </c>
       <c r="G294" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12188,7 +12188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F295" t="str">
-        <v>0.052s</v>
+        <v>0.128s</v>
       </c>
       <c r="G295" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12228,7 +12228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F296" t="str">
-        <v>0.111s</v>
+        <v>0.128s</v>
       </c>
       <c r="G296" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12268,7 +12268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F297" t="str">
-        <v>0.104s</v>
+        <v>0.066s</v>
       </c>
       <c r="G297" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12308,7 +12308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F298" t="str">
-        <v>0.055s</v>
+        <v>0.095s</v>
       </c>
       <c r="G298" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12348,7 +12348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F299" t="str">
-        <v>0.117s</v>
+        <v>0.135s</v>
       </c>
       <c r="G299" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12388,7 +12388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F300" t="str">
-        <v>0.110s</v>
+        <v>0.140s</v>
       </c>
       <c r="G300" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12428,7 +12428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F301" t="str">
-        <v>0.106s</v>
+        <v>0.067s</v>
       </c>
       <c r="G301" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12468,7 +12468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F302" t="str">
-        <v>0.058s</v>
+        <v>0.052s</v>
       </c>
       <c r="G302" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12508,7 +12508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F303" t="str">
-        <v>0.049s</v>
+        <v>0.043s</v>
       </c>
       <c r="G303" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12548,7 +12548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F304" t="str">
-        <v>0.091s</v>
+        <v>0.121s</v>
       </c>
       <c r="G304" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12588,7 +12588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F305" t="str">
-        <v>0.084s</v>
+        <v>0.090s</v>
       </c>
       <c r="G305" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12628,7 +12628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F306" t="str">
-        <v>0.077s</v>
+        <v>0.116s</v>
       </c>
       <c r="G306" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12668,7 +12668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F307" t="str">
-        <v>0.137s</v>
+        <v>0.084s</v>
       </c>
       <c r="G307" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12708,7 +12708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F308" t="str">
-        <v>0.105s</v>
+        <v>0.107s</v>
       </c>
       <c r="G308" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12748,7 +12748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F309" t="str">
-        <v>0.040s</v>
+        <v>0.047s</v>
       </c>
       <c r="G309" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12788,7 +12788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F310" t="str">
-        <v>0.146s</v>
+        <v>0.110s</v>
       </c>
       <c r="G310" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12828,7 +12828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F311" t="str">
-        <v>0.087s</v>
+        <v>0.158s</v>
       </c>
       <c r="G311" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12868,7 +12868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F312" t="str">
-        <v>0.068s</v>
+        <v>0.138s</v>
       </c>
       <c r="G312" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12908,7 +12908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F313" t="str">
-        <v>0.049s</v>
+        <v>0.067s</v>
       </c>
       <c r="G313" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12948,7 +12948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F314" t="str">
-        <v>0.158s</v>
+        <v>0.114s</v>
       </c>
       <c r="G314" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -12988,7 +12988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F315" t="str">
-        <v>0.126s</v>
+        <v>0.100s</v>
       </c>
       <c r="G315" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13028,7 +13028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F316" t="str">
-        <v>0.151s</v>
+        <v>0.085s</v>
       </c>
       <c r="G316" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13068,7 +13068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F317" t="str">
-        <v>0.100s</v>
+        <v>0.074s</v>
       </c>
       <c r="G317" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13108,7 +13108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F318" t="str">
-        <v>0.096s</v>
+        <v>0.112s</v>
       </c>
       <c r="G318" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13148,7 +13148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F319" t="str">
-        <v>0.048s</v>
+        <v>0.146s</v>
       </c>
       <c r="G319" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13188,7 +13188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F320" t="str">
-        <v>0.076s</v>
+        <v>0.111s</v>
       </c>
       <c r="G320" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13228,7 +13228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F321" t="str">
-        <v>0.158s</v>
+        <v>0.101s</v>
       </c>
       <c r="G321" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13268,7 +13268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F322" t="str">
-        <v>0.042s</v>
+        <v>0.095s</v>
       </c>
       <c r="G322" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13308,7 +13308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F323" t="str">
-        <v>0.121s</v>
+        <v>0.071s</v>
       </c>
       <c r="G323" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13348,7 +13348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F324" t="str">
-        <v>0.046s</v>
+        <v>0.055s</v>
       </c>
       <c r="G324" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13388,7 +13388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F325" t="str">
-        <v>0.073s</v>
+        <v>0.128s</v>
       </c>
       <c r="G325" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13428,7 +13428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F326" t="str">
-        <v>0.110s</v>
+        <v>0.071s</v>
       </c>
       <c r="G326" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13468,7 +13468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F327" t="str">
-        <v>0.124s</v>
+        <v>0.095s</v>
       </c>
       <c r="G327" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13508,7 +13508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F328" t="str">
-        <v>0.087s</v>
+        <v>0.047s</v>
       </c>
       <c r="G328" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13548,7 +13548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F329" t="str">
-        <v>0.082s</v>
+        <v>0.090s</v>
       </c>
       <c r="G329" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13588,7 +13588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F330" t="str">
-        <v>0.053s</v>
+        <v>0.113s</v>
       </c>
       <c r="G330" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13628,7 +13628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F331" t="str">
-        <v>0.097s</v>
+        <v>0.081s</v>
       </c>
       <c r="G331" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13668,7 +13668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F332" t="str">
-        <v>0.090s</v>
+        <v>0.105s</v>
       </c>
       <c r="G332" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13708,7 +13708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F333" t="str">
-        <v>0.154s</v>
+        <v>0.053s</v>
       </c>
       <c r="G333" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13748,7 +13748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F334" t="str">
-        <v>0.100s</v>
+        <v>0.046s</v>
       </c>
       <c r="G334" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13788,7 +13788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F335" t="str">
-        <v>0.117s</v>
+        <v>0.074s</v>
       </c>
       <c r="G335" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13828,7 +13828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F336" t="str">
-        <v>0.076s</v>
+        <v>0.125s</v>
       </c>
       <c r="G336" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13868,7 +13868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F337" t="str">
-        <v>0.132s</v>
+        <v>0.074s</v>
       </c>
       <c r="G337" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13908,7 +13908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F338" t="str">
-        <v>0.151s</v>
+        <v>0.131s</v>
       </c>
       <c r="G338" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13948,7 +13948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F339" t="str">
-        <v>0.140s</v>
+        <v>0.074s</v>
       </c>
       <c r="G339" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -13988,7 +13988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F340" t="str">
-        <v>0.155s</v>
+        <v>0.141s</v>
       </c>
       <c r="G340" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14028,7 +14028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F341" t="str">
-        <v>0.042s</v>
+        <v>0.105s</v>
       </c>
       <c r="G341" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14068,7 +14068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F342" t="str">
-        <v>0.117s</v>
+        <v>0.078s</v>
       </c>
       <c r="G342" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14108,7 +14108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F343" t="str">
-        <v>0.122s</v>
+        <v>0.048s</v>
       </c>
       <c r="G343" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14148,7 +14148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F344" t="str">
-        <v>0.055s</v>
+        <v>0.068s</v>
       </c>
       <c r="G344" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14188,7 +14188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F345" t="str">
-        <v>0.065s</v>
+        <v>0.076s</v>
       </c>
       <c r="G345" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14228,7 +14228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F346" t="str">
-        <v>0.076s</v>
+        <v>0.073s</v>
       </c>
       <c r="G346" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14268,7 +14268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F347" t="str">
-        <v>0.134s</v>
+        <v>0.119s</v>
       </c>
       <c r="G347" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14308,7 +14308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F348" t="str">
-        <v>0.070s</v>
+        <v>0.131s</v>
       </c>
       <c r="G348" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14348,7 +14348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F349" t="str">
-        <v>0.071s</v>
+        <v>0.150s</v>
       </c>
       <c r="G349" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14388,7 +14388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F350" t="str">
-        <v>0.044s</v>
+        <v>0.108s</v>
       </c>
       <c r="G350" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14428,7 +14428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F351" t="str">
-        <v>0.129s</v>
+        <v>0.120s</v>
       </c>
       <c r="G351" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14468,7 +14468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F352" t="str">
-        <v>0.083s</v>
+        <v>0.053s</v>
       </c>
       <c r="G352" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14508,7 +14508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F353" t="str">
-        <v>0.099s</v>
+        <v>0.119s</v>
       </c>
       <c r="G353" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14548,7 +14548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F354" t="str">
-        <v>0.058s</v>
+        <v>0.150s</v>
       </c>
       <c r="G354" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14588,7 +14588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F355" t="str">
-        <v>0.077s</v>
+        <v>0.072s</v>
       </c>
       <c r="G355" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14628,7 +14628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F356" t="str">
-        <v>0.056s</v>
+        <v>0.085s</v>
       </c>
       <c r="G356" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14668,7 +14668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F357" t="str">
-        <v>0.109s</v>
+        <v>0.145s</v>
       </c>
       <c r="G357" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14708,7 +14708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F358" t="str">
-        <v>0.148s</v>
+        <v>0.124s</v>
       </c>
       <c r="G358" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14748,7 +14748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F359" t="str">
-        <v>0.040s</v>
+        <v>0.082s</v>
       </c>
       <c r="G359" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14788,7 +14788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F360" t="str">
-        <v>0.119s</v>
+        <v>0.090s</v>
       </c>
       <c r="G360" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14828,7 +14828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F361" t="str">
-        <v>0.040s</v>
+        <v>0.103s</v>
       </c>
       <c r="G361" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14868,7 +14868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F362" t="str">
-        <v>0.134s</v>
+        <v>0.047s</v>
       </c>
       <c r="G362" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14908,7 +14908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F363" t="str">
-        <v>0.106s</v>
+        <v>0.098s</v>
       </c>
       <c r="G363" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14948,7 +14948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F364" t="str">
-        <v>0.091s</v>
+        <v>0.153s</v>
       </c>
       <c r="G364" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -14988,7 +14988,7 @@
         <v>SKIPPED</v>
       </c>
       <c r="F365" t="str">
-        <v>0.105s</v>
+        <v>0.051s</v>
       </c>
       <c r="G365" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15028,7 +15028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F366" t="str">
-        <v>0.131s</v>
+        <v>0.065s</v>
       </c>
       <c r="G366" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15068,7 +15068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F367" t="str">
-        <v>0.063s</v>
+        <v>0.098s</v>
       </c>
       <c r="G367" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15108,7 +15108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F368" t="str">
-        <v>0.146s</v>
+        <v>0.134s</v>
       </c>
       <c r="G368" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15148,7 +15148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F369" t="str">
-        <v>0.154s</v>
+        <v>0.065s</v>
       </c>
       <c r="G369" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15188,7 +15188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F370" t="str">
-        <v>0.083s</v>
+        <v>0.050s</v>
       </c>
       <c r="G370" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15228,7 +15228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F371" t="str">
-        <v>0.135s</v>
+        <v>0.047s</v>
       </c>
       <c r="G371" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15268,7 +15268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F372" t="str">
-        <v>0.050s</v>
+        <v>0.097s</v>
       </c>
       <c r="G372" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15308,7 +15308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F373" t="str">
-        <v>0.135s</v>
+        <v>0.091s</v>
       </c>
       <c r="G373" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15348,7 +15348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F374" t="str">
-        <v>0.128s</v>
+        <v>0.130s</v>
       </c>
       <c r="G374" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15388,7 +15388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F375" t="str">
-        <v>0.141s</v>
+        <v>0.068s</v>
       </c>
       <c r="G375" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15428,7 +15428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F376" t="str">
-        <v>0.110s</v>
+        <v>0.147s</v>
       </c>
       <c r="G376" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15468,7 +15468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F377" t="str">
-        <v>0.047s</v>
+        <v>0.117s</v>
       </c>
       <c r="G377" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15508,7 +15508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F378" t="str">
-        <v>0.123s</v>
+        <v>0.104s</v>
       </c>
       <c r="G378" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15548,7 +15548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F379" t="str">
-        <v>0.132s</v>
+        <v>0.150s</v>
       </c>
       <c r="G379" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15588,7 +15588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F380" t="str">
-        <v>0.064s</v>
+        <v>0.082s</v>
       </c>
       <c r="G380" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15628,7 +15628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F381" t="str">
-        <v>0.072s</v>
+        <v>0.120s</v>
       </c>
       <c r="G381" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15668,7 +15668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F382" t="str">
-        <v>0.157s</v>
+        <v>0.048s</v>
       </c>
       <c r="G382" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15708,7 +15708,7 @@
         <v>FAILED</v>
       </c>
       <c r="F383" t="str">
-        <v>0.064s</v>
+        <v>0.047s</v>
       </c>
       <c r="G383" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15748,7 +15748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F384" t="str">
-        <v>0.160s</v>
+        <v>0.123s</v>
       </c>
       <c r="G384" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15788,7 +15788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F385" t="str">
-        <v>0.128s</v>
+        <v>0.138s</v>
       </c>
       <c r="G385" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15828,7 +15828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F386" t="str">
-        <v>0.066s</v>
+        <v>0.111s</v>
       </c>
       <c r="G386" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15868,7 +15868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F387" t="str">
-        <v>0.056s</v>
+        <v>0.148s</v>
       </c>
       <c r="G387" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15908,7 +15908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F388" t="str">
-        <v>0.116s</v>
+        <v>0.047s</v>
       </c>
       <c r="G388" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15948,7 +15948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F389" t="str">
-        <v>0.155s</v>
+        <v>0.117s</v>
       </c>
       <c r="G389" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -15988,7 +15988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F390" t="str">
-        <v>0.073s</v>
+        <v>0.127s</v>
       </c>
       <c r="G390" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16028,7 +16028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F391" t="str">
-        <v>0.125s</v>
+        <v>0.084s</v>
       </c>
       <c r="G391" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16068,7 +16068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F392" t="str">
-        <v>0.117s</v>
+        <v>0.131s</v>
       </c>
       <c r="G392" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16108,7 +16108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F393" t="str">
-        <v>0.062s</v>
+        <v>0.150s</v>
       </c>
       <c r="G393" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16148,7 +16148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F394" t="str">
-        <v>0.079s</v>
+        <v>0.070s</v>
       </c>
       <c r="G394" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16188,7 +16188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F395" t="str">
-        <v>0.160s</v>
+        <v>0.104s</v>
       </c>
       <c r="G395" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16228,7 +16228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F396" t="str">
-        <v>0.075s</v>
+        <v>0.120s</v>
       </c>
       <c r="G396" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16268,7 +16268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F397" t="str">
-        <v>0.143s</v>
+        <v>0.079s</v>
       </c>
       <c r="G397" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16308,7 +16308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F398" t="str">
-        <v>0.105s</v>
+        <v>0.133s</v>
       </c>
       <c r="G398" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16348,7 +16348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F399" t="str">
-        <v>0.143s</v>
+        <v>0.113s</v>
       </c>
       <c r="G399" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16388,7 +16388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F400" t="str">
-        <v>0.050s</v>
+        <v>0.067s</v>
       </c>
       <c r="G400" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16428,7 +16428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F401" t="str">
-        <v>0.138s</v>
+        <v>0.119s</v>
       </c>
       <c r="G401" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16468,7 +16468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F402" t="str">
-        <v>0.120s</v>
+        <v>0.097s</v>
       </c>
       <c r="G402" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16508,7 +16508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F403" t="str">
-        <v>0.109s</v>
+        <v>0.054s</v>
       </c>
       <c r="G403" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16548,7 +16548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F404" t="str">
-        <v>0.078s</v>
+        <v>0.061s</v>
       </c>
       <c r="G404" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16588,7 +16588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F405" t="str">
-        <v>0.125s</v>
+        <v>0.109s</v>
       </c>
       <c r="G405" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16628,7 +16628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F406" t="str">
-        <v>0.096s</v>
+        <v>0.057s</v>
       </c>
       <c r="G406" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16668,7 +16668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F407" t="str">
-        <v>0.060s</v>
+        <v>0.064s</v>
       </c>
       <c r="G407" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16708,7 +16708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F408" t="str">
-        <v>0.092s</v>
+        <v>0.112s</v>
       </c>
       <c r="G408" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16748,7 +16748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F409" t="str">
-        <v>0.100s</v>
+        <v>0.118s</v>
       </c>
       <c r="G409" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16788,7 +16788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F410" t="str">
-        <v>0.130s</v>
+        <v>0.104s</v>
       </c>
       <c r="G410" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16828,7 +16828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F411" t="str">
-        <v>0.130s</v>
+        <v>0.110s</v>
       </c>
       <c r="G411" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16868,7 +16868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F412" t="str">
-        <v>0.107s</v>
+        <v>0.089s</v>
       </c>
       <c r="G412" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16908,7 +16908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F413" t="str">
-        <v>0.045s</v>
+        <v>0.080s</v>
       </c>
       <c r="G413" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16948,7 +16948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F414" t="str">
-        <v>0.047s</v>
+        <v>0.109s</v>
       </c>
       <c r="G414" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -16988,7 +16988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F415" t="str">
-        <v>0.130s</v>
+        <v>0.054s</v>
       </c>
       <c r="G415" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17028,7 +17028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F416" t="str">
-        <v>0.138s</v>
+        <v>0.142s</v>
       </c>
       <c r="G416" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17068,7 +17068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F417" t="str">
-        <v>0.142s</v>
+        <v>0.056s</v>
       </c>
       <c r="G417" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17108,7 +17108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F418" t="str">
-        <v>0.091s</v>
+        <v>0.135s</v>
       </c>
       <c r="G418" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17148,7 +17148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F419" t="str">
-        <v>0.131s</v>
+        <v>0.058s</v>
       </c>
       <c r="G419" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17188,7 +17188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F420" t="str">
-        <v>0.143s</v>
+        <v>0.137s</v>
       </c>
       <c r="G420" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17228,7 +17228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F421" t="str">
-        <v>0.043s</v>
+        <v>0.088s</v>
       </c>
       <c r="G421" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17268,7 +17268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F422" t="str">
-        <v>0.152s</v>
+        <v>0.119s</v>
       </c>
       <c r="G422" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17308,7 +17308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F423" t="str">
-        <v>0.083s</v>
+        <v>0.127s</v>
       </c>
       <c r="G423" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17348,7 +17348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F424" t="str">
-        <v>0.084s</v>
+        <v>0.096s</v>
       </c>
       <c r="G424" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17388,7 +17388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F425" t="str">
-        <v>0.071s</v>
+        <v>0.132s</v>
       </c>
       <c r="G425" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17428,7 +17428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F426" t="str">
-        <v>0.125s</v>
+        <v>0.128s</v>
       </c>
       <c r="G426" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17468,7 +17468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F427" t="str">
-        <v>0.105s</v>
+        <v>0.088s</v>
       </c>
       <c r="G427" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17508,7 +17508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F428" t="str">
-        <v>0.124s</v>
+        <v>0.079s</v>
       </c>
       <c r="G428" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17548,7 +17548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F429" t="str">
-        <v>0.081s</v>
+        <v>0.078s</v>
       </c>
       <c r="G429" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17588,7 +17588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F430" t="str">
-        <v>0.136s</v>
+        <v>0.091s</v>
       </c>
       <c r="G430" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17628,7 +17628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F431" t="str">
-        <v>0.059s</v>
+        <v>0.103s</v>
       </c>
       <c r="G431" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17668,7 +17668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F432" t="str">
-        <v>0.085s</v>
+        <v>0.127s</v>
       </c>
       <c r="G432" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17708,7 +17708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F433" t="str">
-        <v>0.113s</v>
+        <v>0.044s</v>
       </c>
       <c r="G433" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17748,7 +17748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F434" t="str">
-        <v>0.043s</v>
+        <v>0.126s</v>
       </c>
       <c r="G434" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17788,7 +17788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F435" t="str">
-        <v>0.087s</v>
+        <v>0.053s</v>
       </c>
       <c r="G435" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17828,7 +17828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F436" t="str">
-        <v>0.059s</v>
+        <v>0.139s</v>
       </c>
       <c r="G436" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17868,7 +17868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F437" t="str">
-        <v>0.062s</v>
+        <v>0.110s</v>
       </c>
       <c r="G437" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17908,7 +17908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F438" t="str">
-        <v>0.070s</v>
+        <v>0.054s</v>
       </c>
       <c r="G438" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17948,7 +17948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F439" t="str">
-        <v>0.097s</v>
+        <v>0.068s</v>
       </c>
       <c r="G439" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -17988,7 +17988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F440" t="str">
-        <v>0.070s</v>
+        <v>0.082s</v>
       </c>
       <c r="G440" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18028,7 +18028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F441" t="str">
-        <v>0.095s</v>
+        <v>0.060s</v>
       </c>
       <c r="G441" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18068,7 +18068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F442" t="str">
-        <v>0.145s</v>
+        <v>0.127s</v>
       </c>
       <c r="G442" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18108,7 +18108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F443" t="str">
-        <v>0.130s</v>
+        <v>0.088s</v>
       </c>
       <c r="G443" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18148,7 +18148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F444" t="str">
-        <v>0.154s</v>
+        <v>0.121s</v>
       </c>
       <c r="G444" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18188,7 +18188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F445" t="str">
-        <v>0.074s</v>
+        <v>0.132s</v>
       </c>
       <c r="G445" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18228,7 +18228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F446" t="str">
-        <v>0.065s</v>
+        <v>0.128s</v>
       </c>
       <c r="G446" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18268,7 +18268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F447" t="str">
-        <v>0.057s</v>
+        <v>0.116s</v>
       </c>
       <c r="G447" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18308,7 +18308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F448" t="str">
-        <v>0.093s</v>
+        <v>0.157s</v>
       </c>
       <c r="G448" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18348,7 +18348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F449" t="str">
-        <v>0.154s</v>
+        <v>0.062s</v>
       </c>
       <c r="G449" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18428,7 +18428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F451" t="str">
-        <v>0.157s</v>
+        <v>0.123s</v>
       </c>
       <c r="G451" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18468,7 +18468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F452" t="str">
-        <v>0.067s</v>
+        <v>0.100s</v>
       </c>
       <c r="G452" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18508,7 +18508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F453" t="str">
-        <v>0.062s</v>
+        <v>0.128s</v>
       </c>
       <c r="G453" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18548,7 +18548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F454" t="str">
-        <v>0.159s</v>
+        <v>0.150s</v>
       </c>
       <c r="G454" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18588,7 +18588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F455" t="str">
-        <v>0.151s</v>
+        <v>0.127s</v>
       </c>
       <c r="G455" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18628,7 +18628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F456" t="str">
-        <v>0.138s</v>
+        <v>0.082s</v>
       </c>
       <c r="G456" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18668,7 +18668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F457" t="str">
-        <v>0.087s</v>
+        <v>0.070s</v>
       </c>
       <c r="G457" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18708,7 +18708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F458" t="str">
-        <v>0.105s</v>
+        <v>0.148s</v>
       </c>
       <c r="G458" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18748,7 +18748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F459" t="str">
-        <v>0.078s</v>
+        <v>0.096s</v>
       </c>
       <c r="G459" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18788,7 +18788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F460" t="str">
-        <v>0.096s</v>
+        <v>0.156s</v>
       </c>
       <c r="G460" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18828,7 +18828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F461" t="str">
-        <v>0.107s</v>
+        <v>0.140s</v>
       </c>
       <c r="G461" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18868,7 +18868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F462" t="str">
-        <v>0.098s</v>
+        <v>0.153s</v>
       </c>
       <c r="G462" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18908,7 +18908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F463" t="str">
-        <v>0.096s</v>
+        <v>0.151s</v>
       </c>
       <c r="G463" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18948,7 +18948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F464" t="str">
-        <v>0.158s</v>
+        <v>0.124s</v>
       </c>
       <c r="G464" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -18988,7 +18988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F465" t="str">
-        <v>0.108s</v>
+        <v>0.137s</v>
       </c>
       <c r="G465" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19028,7 +19028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F466" t="str">
-        <v>0.091s</v>
+        <v>0.154s</v>
       </c>
       <c r="G466" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19068,7 +19068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F467" t="str">
-        <v>0.081s</v>
+        <v>0.077s</v>
       </c>
       <c r="G467" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19108,7 +19108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F468" t="str">
-        <v>0.154s</v>
+        <v>0.115s</v>
       </c>
       <c r="G468" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19148,7 +19148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F469" t="str">
-        <v>0.074s</v>
+        <v>0.103s</v>
       </c>
       <c r="G469" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19188,7 +19188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F470" t="str">
-        <v>0.045s</v>
+        <v>0.087s</v>
       </c>
       <c r="G470" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19228,7 +19228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F471" t="str">
-        <v>0.050s</v>
+        <v>0.141s</v>
       </c>
       <c r="G471" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19268,7 +19268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F472" t="str">
-        <v>0.061s</v>
+        <v>0.151s</v>
       </c>
       <c r="G472" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19308,7 +19308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F473" t="str">
-        <v>0.067s</v>
+        <v>0.097s</v>
       </c>
       <c r="G473" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19348,7 +19348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F474" t="str">
-        <v>0.107s</v>
+        <v>0.064s</v>
       </c>
       <c r="G474" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19388,7 +19388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F475" t="str">
-        <v>0.067s</v>
+        <v>0.148s</v>
       </c>
       <c r="G475" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19428,7 +19428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F476" t="str">
-        <v>0.125s</v>
+        <v>0.072s</v>
       </c>
       <c r="G476" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19468,7 +19468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F477" t="str">
-        <v>0.145s</v>
+        <v>0.107s</v>
       </c>
       <c r="G477" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19508,7 +19508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F478" t="str">
-        <v>0.147s</v>
+        <v>0.041s</v>
       </c>
       <c r="G478" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19548,7 +19548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F479" t="str">
-        <v>0.062s</v>
+        <v>0.058s</v>
       </c>
       <c r="G479" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19588,7 +19588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F480" t="str">
-        <v>0.092s</v>
+        <v>0.064s</v>
       </c>
       <c r="G480" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19628,7 +19628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F481" t="str">
-        <v>0.141s</v>
+        <v>0.081s</v>
       </c>
       <c r="G481" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19668,7 +19668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F482" t="str">
-        <v>0.073s</v>
+        <v>0.147s</v>
       </c>
       <c r="G482" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19708,7 +19708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F483" t="str">
-        <v>0.101s</v>
+        <v>0.140s</v>
       </c>
       <c r="G483" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19748,7 +19748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F484" t="str">
-        <v>0.081s</v>
+        <v>0.046s</v>
       </c>
       <c r="G484" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19788,7 +19788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F485" t="str">
-        <v>0.063s</v>
+        <v>0.081s</v>
       </c>
       <c r="G485" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19828,7 +19828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F486" t="str">
-        <v>0.145s</v>
+        <v>0.103s</v>
       </c>
       <c r="G486" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19868,7 +19868,7 @@
         <v>PASSED</v>
       </c>
       <c r="F487" t="str">
-        <v>0.075s</v>
+        <v>0.073s</v>
       </c>
       <c r="G487" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19908,7 +19908,7 @@
         <v>PASSED</v>
       </c>
       <c r="F488" t="str">
-        <v>0.068s</v>
+        <v>0.094s</v>
       </c>
       <c r="G488" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19948,7 +19948,7 @@
         <v>PASSED</v>
       </c>
       <c r="F489" t="str">
-        <v>0.156s</v>
+        <v>0.047s</v>
       </c>
       <c r="G489" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -19988,7 +19988,7 @@
         <v>PASSED</v>
       </c>
       <c r="F490" t="str">
-        <v>0.156s</v>
+        <v>0.077s</v>
       </c>
       <c r="G490" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20028,7 +20028,7 @@
         <v>PASSED</v>
       </c>
       <c r="F491" t="str">
-        <v>0.090s</v>
+        <v>0.124s</v>
       </c>
       <c r="G491" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20068,7 +20068,7 @@
         <v>PASSED</v>
       </c>
       <c r="F492" t="str">
-        <v>0.122s</v>
+        <v>0.044s</v>
       </c>
       <c r="G492" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20108,7 +20108,7 @@
         <v>PASSED</v>
       </c>
       <c r="F493" t="str">
-        <v>0.069s</v>
+        <v>0.155s</v>
       </c>
       <c r="G493" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20148,7 +20148,7 @@
         <v>PASSED</v>
       </c>
       <c r="F494" t="str">
-        <v>0.098s</v>
+        <v>0.076s</v>
       </c>
       <c r="G494" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20188,7 +20188,7 @@
         <v>PASSED</v>
       </c>
       <c r="F495" t="str">
-        <v>0.069s</v>
+        <v>0.091s</v>
       </c>
       <c r="G495" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20228,7 +20228,7 @@
         <v>PASSED</v>
       </c>
       <c r="F496" t="str">
-        <v>0.050s</v>
+        <v>0.091s</v>
       </c>
       <c r="G496" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20268,7 +20268,7 @@
         <v>PASSED</v>
       </c>
       <c r="F497" t="str">
-        <v>0.056s</v>
+        <v>0.052s</v>
       </c>
       <c r="G497" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20308,7 +20308,7 @@
         <v>PASSED</v>
       </c>
       <c r="F498" t="str">
-        <v>0.090s</v>
+        <v>0.133s</v>
       </c>
       <c r="G498" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20348,7 +20348,7 @@
         <v>PASSED</v>
       </c>
       <c r="F499" t="str">
-        <v>0.098s</v>
+        <v>0.074s</v>
       </c>
       <c r="G499" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20388,7 +20388,7 @@
         <v>PASSED</v>
       </c>
       <c r="F500" t="str">
-        <v>0.146s</v>
+        <v>0.117s</v>
       </c>
       <c r="G500" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20428,7 +20428,7 @@
         <v>PASSED</v>
       </c>
       <c r="F501" t="str">
-        <v>0.140s</v>
+        <v>0.083s</v>
       </c>
       <c r="G501" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20468,7 +20468,7 @@
         <v>PASSED</v>
       </c>
       <c r="F502" t="str">
-        <v>0.081s</v>
+        <v>0.094s</v>
       </c>
       <c r="G502" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20508,7 +20508,7 @@
         <v>PASSED</v>
       </c>
       <c r="F503" t="str">
-        <v>0.102s</v>
+        <v>0.080s</v>
       </c>
       <c r="G503" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20548,7 +20548,7 @@
         <v>PASSED</v>
       </c>
       <c r="F504" t="str">
-        <v>0.141s</v>
+        <v>0.125s</v>
       </c>
       <c r="G504" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20588,7 +20588,7 @@
         <v>PASSED</v>
       </c>
       <c r="F505" t="str">
-        <v>0.069s</v>
+        <v>0.095s</v>
       </c>
       <c r="G505" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20628,7 +20628,7 @@
         <v>PASSED</v>
       </c>
       <c r="F506" t="str">
-        <v>0.159s</v>
+        <v>0.141s</v>
       </c>
       <c r="G506" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20668,7 +20668,7 @@
         <v>PASSED</v>
       </c>
       <c r="F507" t="str">
-        <v>0.074s</v>
+        <v>0.141s</v>
       </c>
       <c r="G507" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20708,7 +20708,7 @@
         <v>PASSED</v>
       </c>
       <c r="F508" t="str">
-        <v>0.125s</v>
+        <v>0.103s</v>
       </c>
       <c r="G508" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20748,7 +20748,7 @@
         <v>PASSED</v>
       </c>
       <c r="F509" t="str">
-        <v>0.041s</v>
+        <v>0.098s</v>
       </c>
       <c r="G509" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20788,7 +20788,7 @@
         <v>PASSED</v>
       </c>
       <c r="F510" t="str">
-        <v>0.126s</v>
+        <v>0.053s</v>
       </c>
       <c r="G510" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20828,7 +20828,7 @@
         <v>PASSED</v>
       </c>
       <c r="F511" t="str">
-        <v>0.139s</v>
+        <v>0.138s</v>
       </c>
       <c r="G511" t="str">
         <v>Android APK installed on emulator/device, Appium UiAutomator2 session active.</v>
@@ -20893,7 +20893,7 @@
         <v>LOW</v>
       </c>
       <c r="E2" t="str">
-        <v>0.059s</v>
+        <v>0.137s</v>
       </c>
     </row>
     <row r="3">
@@ -20910,7 +20910,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E3" t="str">
-        <v>0.153s</v>
+        <v>0.143s</v>
       </c>
     </row>
     <row r="4">
@@ -20927,7 +20927,7 @@
         <v>HIGH</v>
       </c>
       <c r="E4" t="str">
-        <v>0.108s</v>
+        <v>0.117s</v>
       </c>
     </row>
     <row r="5">
@@ -20944,7 +20944,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E5" t="str">
-        <v>0.140s</v>
+        <v>0.057s</v>
       </c>
     </row>
     <row r="6">
@@ -20961,7 +20961,7 @@
         <v>LOW</v>
       </c>
       <c r="E6" t="str">
-        <v>0.096s</v>
+        <v>0.118s</v>
       </c>
     </row>
     <row r="7">
@@ -20978,7 +20978,7 @@
         <v>HIGH</v>
       </c>
       <c r="E7" t="str">
-        <v>0.069s</v>
+        <v>0.064s</v>
       </c>
     </row>
     <row r="8">
@@ -20995,7 +20995,7 @@
         <v>LOW</v>
       </c>
       <c r="E8" t="str">
-        <v>0.068s</v>
+        <v>0.070s</v>
       </c>
     </row>
     <row r="9">
@@ -21012,7 +21012,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E9" t="str">
-        <v>0.057s</v>
+        <v>0.069s</v>
       </c>
     </row>
     <row r="10">
@@ -21029,7 +21029,7 @@
         <v>HIGH</v>
       </c>
       <c r="E10" t="str">
-        <v>0.094s</v>
+        <v>0.137s</v>
       </c>
     </row>
     <row r="11">
@@ -21046,7 +21046,7 @@
         <v>LOW</v>
       </c>
       <c r="E11" t="str">
-        <v>0.143s</v>
+        <v>0.093s</v>
       </c>
     </row>
     <row r="12">
@@ -21063,7 +21063,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E12" t="str">
-        <v>0.056s</v>
+        <v>0.044s</v>
       </c>
     </row>
     <row r="13">
@@ -21080,7 +21080,7 @@
         <v>LOW</v>
       </c>
       <c r="E13" t="str">
-        <v>0.155s</v>
+        <v>0.059s</v>
       </c>
     </row>
     <row r="14">
@@ -21097,7 +21097,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E14" t="str">
-        <v>0.043s</v>
+        <v>0.065s</v>
       </c>
     </row>
     <row r="15">
@@ -21114,7 +21114,7 @@
         <v>HIGH</v>
       </c>
       <c r="E15" t="str">
-        <v>0.060s</v>
+        <v>0.097s</v>
       </c>
     </row>
     <row r="16">
@@ -21131,7 +21131,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E16" t="str">
-        <v>0.113s</v>
+        <v>0.076s</v>
       </c>
     </row>
     <row r="17">
@@ -21148,7 +21148,7 @@
         <v>LOW</v>
       </c>
       <c r="E17" t="str">
-        <v>0.060s</v>
+        <v>0.087s</v>
       </c>
     </row>
     <row r="18">
@@ -21165,7 +21165,7 @@
         <v>HIGH</v>
       </c>
       <c r="E18" t="str">
-        <v>0.057s</v>
+        <v>0.146s</v>
       </c>
     </row>
     <row r="19">
@@ -21182,7 +21182,7 @@
         <v>LOW</v>
       </c>
       <c r="E19" t="str">
-        <v>0.141s</v>
+        <v>0.100s</v>
       </c>
     </row>
     <row r="20">
@@ -21199,7 +21199,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E20" t="str">
-        <v>0.119s</v>
+        <v>0.043s</v>
       </c>
     </row>
     <row r="21">
@@ -21216,7 +21216,7 @@
         <v>HIGH</v>
       </c>
       <c r="E21" t="str">
-        <v>0.109s</v>
+        <v>0.148s</v>
       </c>
     </row>
     <row r="22">
@@ -21233,7 +21233,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E22" t="str">
-        <v>0.073s</v>
+        <v>0.095s</v>
       </c>
     </row>
     <row r="23">
@@ -21250,7 +21250,7 @@
         <v>LOW</v>
       </c>
       <c r="E23" t="str">
-        <v>0.083s</v>
+        <v>0.082s</v>
       </c>
     </row>
     <row r="24">
@@ -21267,7 +21267,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E24" t="str">
-        <v>0.047s</v>
+        <v>0.055s</v>
       </c>
     </row>
     <row r="25">
@@ -21284,7 +21284,7 @@
         <v>LOW</v>
       </c>
       <c r="E25" t="str">
-        <v>0.047s</v>
+        <v>0.149s</v>
       </c>
     </row>
     <row r="26">
@@ -21301,7 +21301,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E26" t="str">
-        <v>0.095s</v>
+        <v>0.044s</v>
       </c>
     </row>
     <row r="27">
@@ -21335,7 +21335,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E28" t="str">
-        <v>0.044s</v>
+        <v>0.073s</v>
       </c>
     </row>
     <row r="29">
@@ -21352,7 +21352,7 @@
         <v>LOW</v>
       </c>
       <c r="E29" t="str">
-        <v>0.160s</v>
+        <v>0.106s</v>
       </c>
     </row>
     <row r="30">
@@ -21369,7 +21369,7 @@
         <v>HIGH</v>
       </c>
       <c r="E30" t="str">
-        <v>0.090s</v>
+        <v>0.066s</v>
       </c>
     </row>
     <row r="31">
@@ -21386,7 +21386,7 @@
         <v>LOW</v>
       </c>
       <c r="E31" t="str">
-        <v>0.051s</v>
+        <v>0.151s</v>
       </c>
     </row>
     <row r="32">
@@ -21403,7 +21403,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E32" t="str">
-        <v>0.063s</v>
+        <v>0.088s</v>
       </c>
     </row>
     <row r="33">
@@ -21420,7 +21420,7 @@
         <v>HIGH</v>
       </c>
       <c r="E33" t="str">
-        <v>0.081s</v>
+        <v>0.125s</v>
       </c>
     </row>
     <row r="34">
@@ -21437,7 +21437,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E34" t="str">
-        <v>0.141s</v>
+        <v>0.067s</v>
       </c>
     </row>
     <row r="35">
@@ -21454,7 +21454,7 @@
         <v>LOW</v>
       </c>
       <c r="E35" t="str">
-        <v>0.077s</v>
+        <v>0.102s</v>
       </c>
     </row>
     <row r="36">
@@ -21471,7 +21471,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E36" t="str">
-        <v>0.066s</v>
+        <v>0.153s</v>
       </c>
     </row>
     <row r="37">
@@ -21488,7 +21488,7 @@
         <v>LOW</v>
       </c>
       <c r="E37" t="str">
-        <v>0.133s</v>
+        <v>0.071s</v>
       </c>
     </row>
     <row r="38">
@@ -21505,7 +21505,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E38" t="str">
-        <v>0.153s</v>
+        <v>0.134s</v>
       </c>
     </row>
     <row r="39">
@@ -21522,7 +21522,7 @@
         <v>HIGH</v>
       </c>
       <c r="E39" t="str">
-        <v>0.061s</v>
+        <v>0.084s</v>
       </c>
     </row>
     <row r="40">
@@ -21539,7 +21539,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E40" t="str">
-        <v>0.120s</v>
+        <v>0.099s</v>
       </c>
     </row>
     <row r="41">
@@ -21556,7 +21556,7 @@
         <v>LOW</v>
       </c>
       <c r="E41" t="str">
-        <v>0.095s</v>
+        <v>0.055s</v>
       </c>
     </row>
     <row r="42">
@@ -21573,7 +21573,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E42" t="str">
-        <v>0.077s</v>
+        <v>0.075s</v>
       </c>
     </row>
     <row r="43">
@@ -21590,7 +21590,7 @@
         <v>HIGH</v>
       </c>
       <c r="E43" t="str">
-        <v>0.139s</v>
+        <v>0.157s</v>
       </c>
     </row>
     <row r="44">
@@ -21607,7 +21607,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E44" t="str">
-        <v>0.146s</v>
+        <v>0.057s</v>
       </c>
     </row>
     <row r="45">
@@ -21624,7 +21624,7 @@
         <v>LOW</v>
       </c>
       <c r="E45" t="str">
-        <v>0.098s</v>
+        <v>0.145s</v>
       </c>
     </row>
     <row r="46">
@@ -21641,7 +21641,7 @@
         <v>HIGH</v>
       </c>
       <c r="E46" t="str">
-        <v>0.089s</v>
+        <v>0.149s</v>
       </c>
     </row>
     <row r="47">
@@ -21658,7 +21658,7 @@
         <v>LOW</v>
       </c>
       <c r="E47" t="str">
-        <v>0.089s</v>
+        <v>0.103s</v>
       </c>
     </row>
     <row r="48">
@@ -21675,7 +21675,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E48" t="str">
-        <v>0.077s</v>
+        <v>0.082s</v>
       </c>
     </row>
     <row r="49">
@@ -21692,7 +21692,7 @@
         <v>HIGH</v>
       </c>
       <c r="E49" t="str">
-        <v>0.138s</v>
+        <v>0.117s</v>
       </c>
     </row>
     <row r="50">
@@ -21709,7 +21709,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E50" t="str">
-        <v>0.062s</v>
+        <v>0.131s</v>
       </c>
     </row>
     <row r="51">
@@ -21726,7 +21726,7 @@
         <v>LOW</v>
       </c>
       <c r="E51" t="str">
-        <v>0.105s</v>
+        <v>0.092s</v>
       </c>
     </row>
     <row r="52">
@@ -21743,7 +21743,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E52" t="str">
-        <v>0.078s</v>
+        <v>0.139s</v>
       </c>
     </row>
     <row r="53">
@@ -21760,7 +21760,7 @@
         <v>LOW</v>
       </c>
       <c r="E53" t="str">
-        <v>0.061s</v>
+        <v>0.057s</v>
       </c>
     </row>
     <row r="54">
@@ -21777,7 +21777,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E54" t="str">
-        <v>0.139s</v>
+        <v>0.152s</v>
       </c>
     </row>
     <row r="55">
@@ -21794,7 +21794,7 @@
         <v>HIGH</v>
       </c>
       <c r="E55" t="str">
-        <v>0.060s</v>
+        <v>0.062s</v>
       </c>
     </row>
     <row r="56">
@@ -21811,7 +21811,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E56" t="str">
-        <v>0.066s</v>
+        <v>0.142s</v>
       </c>
     </row>
     <row r="57">
@@ -21828,7 +21828,7 @@
         <v>LOW</v>
       </c>
       <c r="E57" t="str">
-        <v>0.092s</v>
+        <v>0.130s</v>
       </c>
     </row>
     <row r="58">
@@ -21845,7 +21845,7 @@
         <v>HIGH</v>
       </c>
       <c r="E58" t="str">
-        <v>0.117s</v>
+        <v>0.041s</v>
       </c>
     </row>
     <row r="59">
@@ -21862,7 +21862,7 @@
         <v>LOW</v>
       </c>
       <c r="E59" t="str">
-        <v>0.157s</v>
+        <v>0.129s</v>
       </c>
     </row>
     <row r="60">
@@ -21879,7 +21879,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E60" t="str">
-        <v>0.130s</v>
+        <v>0.133s</v>
       </c>
     </row>
     <row r="61">
@@ -21896,7 +21896,7 @@
         <v>HIGH</v>
       </c>
       <c r="E61" t="str">
-        <v>0.115s</v>
+        <v>0.063s</v>
       </c>
     </row>
     <row r="62">
@@ -21913,7 +21913,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E62" t="str">
-        <v>0.118s</v>
+        <v>0.122s</v>
       </c>
     </row>
     <row r="63">
@@ -21930,7 +21930,7 @@
         <v>LOW</v>
       </c>
       <c r="E63" t="str">
-        <v>0.089s</v>
+        <v>0.094s</v>
       </c>
     </row>
     <row r="64">
@@ -21947,7 +21947,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E64" t="str">
-        <v>0.063s</v>
+        <v>0.147s</v>
       </c>
     </row>
     <row r="65">
@@ -21964,7 +21964,7 @@
         <v>LOW</v>
       </c>
       <c r="E65" t="str">
-        <v>0.134s</v>
+        <v>0.046s</v>
       </c>
     </row>
     <row r="66">
@@ -21981,7 +21981,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E66" t="str">
-        <v>0.045s</v>
+        <v>0.062s</v>
       </c>
     </row>
     <row r="67">
@@ -21998,7 +21998,7 @@
         <v>HIGH</v>
       </c>
       <c r="E67" t="str">
-        <v>0.052s</v>
+        <v>0.155s</v>
       </c>
     </row>
     <row r="68">
@@ -22015,7 +22015,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E68" t="str">
-        <v>0.047s</v>
+        <v>0.065s</v>
       </c>
     </row>
     <row r="69">
@@ -22032,7 +22032,7 @@
         <v>LOW</v>
       </c>
       <c r="E69" t="str">
-        <v>0.138s</v>
+        <v>0.083s</v>
       </c>
     </row>
     <row r="70">
@@ -22049,7 +22049,7 @@
         <v>HIGH</v>
       </c>
       <c r="E70" t="str">
-        <v>0.062s</v>
+        <v>0.121s</v>
       </c>
     </row>
     <row r="71">
@@ -22066,7 +22066,7 @@
         <v>LOW</v>
       </c>
       <c r="E71" t="str">
-        <v>0.072s</v>
+        <v>0.073s</v>
       </c>
     </row>
     <row r="72">
@@ -22083,7 +22083,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E72" t="str">
-        <v>0.116s</v>
+        <v>0.049s</v>
       </c>
     </row>
     <row r="73">
@@ -22100,7 +22100,7 @@
         <v>HIGH</v>
       </c>
       <c r="E73" t="str">
-        <v>0.071s</v>
+        <v>0.098s</v>
       </c>
     </row>
     <row r="74">
@@ -22117,7 +22117,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E74" t="str">
-        <v>0.051s</v>
+        <v>0.132s</v>
       </c>
     </row>
     <row r="75">
@@ -22134,7 +22134,7 @@
         <v>LOW</v>
       </c>
       <c r="E75" t="str">
-        <v>0.080s</v>
+        <v>0.139s</v>
       </c>
     </row>
     <row r="76">
@@ -22151,7 +22151,7 @@
         <v>HIGH</v>
       </c>
       <c r="E76" t="str">
-        <v>0.114s</v>
+        <v>0.112s</v>
       </c>
     </row>
     <row r="77">
@@ -22168,7 +22168,7 @@
         <v>LOW</v>
       </c>
       <c r="E77" t="str">
-        <v>0.121s</v>
+        <v>0.076s</v>
       </c>
     </row>
     <row r="78">
@@ -22185,7 +22185,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E78" t="str">
-        <v>0.072s</v>
+        <v>0.155s</v>
       </c>
     </row>
     <row r="79">
@@ -22202,7 +22202,7 @@
         <v>HIGH</v>
       </c>
       <c r="E79" t="str">
-        <v>0.077s</v>
+        <v>0.083s</v>
       </c>
     </row>
     <row r="80">
@@ -22219,7 +22219,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E80" t="str">
-        <v>0.155s</v>
+        <v>0.078s</v>
       </c>
     </row>
     <row r="81">
@@ -22236,7 +22236,7 @@
         <v>LOW</v>
       </c>
       <c r="E81" t="str">
-        <v>0.108s</v>
+        <v>0.052s</v>
       </c>
     </row>
     <row r="82">
@@ -22253,7 +22253,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E82" t="str">
-        <v>0.124s</v>
+        <v>0.150s</v>
       </c>
     </row>
     <row r="83">
@@ -22270,7 +22270,7 @@
         <v>LOW</v>
       </c>
       <c r="E83" t="str">
-        <v>0.047s</v>
+        <v>0.086s</v>
       </c>
     </row>
     <row r="84">
@@ -22287,7 +22287,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E84" t="str">
-        <v>0.121s</v>
+        <v>0.093s</v>
       </c>
     </row>
     <row r="85">
@@ -22304,7 +22304,7 @@
         <v>HIGH</v>
       </c>
       <c r="E85" t="str">
-        <v>0.051s</v>
+        <v>0.147s</v>
       </c>
     </row>
     <row r="86">
@@ -22321,7 +22321,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E86" t="str">
-        <v>0.055s</v>
+        <v>0.057s</v>
       </c>
     </row>
     <row r="87">
@@ -22338,7 +22338,7 @@
         <v>LOW</v>
       </c>
       <c r="E87" t="str">
-        <v>0.148s</v>
+        <v>0.055s</v>
       </c>
     </row>
     <row r="88">
@@ -22355,7 +22355,7 @@
         <v>HIGH</v>
       </c>
       <c r="E88" t="str">
-        <v>0.088s</v>
+        <v>0.055s</v>
       </c>
     </row>
     <row r="89">
@@ -22372,7 +22372,7 @@
         <v>LOW</v>
       </c>
       <c r="E89" t="str">
-        <v>0.138s</v>
+        <v>0.148s</v>
       </c>
     </row>
     <row r="90">
@@ -22389,7 +22389,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E90" t="str">
-        <v>0.156s</v>
+        <v>0.068s</v>
       </c>
     </row>
     <row r="91">
@@ -22406,7 +22406,7 @@
         <v>LOW</v>
       </c>
       <c r="E91" t="str">
-        <v>0.127s</v>
+        <v>0.138s</v>
       </c>
     </row>
     <row r="92">
@@ -22423,7 +22423,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E92" t="str">
-        <v>0.139s</v>
+        <v>0.071s</v>
       </c>
     </row>
     <row r="93">
@@ -22440,7 +22440,7 @@
         <v>HIGH</v>
       </c>
       <c r="E93" t="str">
-        <v>0.160s</v>
+        <v>0.048s</v>
       </c>
     </row>
     <row r="94">
@@ -22457,7 +22457,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E94" t="str">
-        <v>0.043s</v>
+        <v>0.142s</v>
       </c>
     </row>
     <row r="95">
@@ -22474,7 +22474,7 @@
         <v>LOW</v>
       </c>
       <c r="E95" t="str">
-        <v>0.145s</v>
+        <v>0.087s</v>
       </c>
     </row>
     <row r="96">
@@ -22491,7 +22491,7 @@
         <v>HIGH</v>
       </c>
       <c r="E96" t="str">
-        <v>0.091s</v>
+        <v>0.058s</v>
       </c>
     </row>
     <row r="97">
@@ -22508,7 +22508,7 @@
         <v>LOW</v>
       </c>
       <c r="E97" t="str">
-        <v>0.071s</v>
+        <v>0.104s</v>
       </c>
     </row>
     <row r="98">
@@ -22525,7 +22525,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E98" t="str">
-        <v>0.077s</v>
+        <v>0.089s</v>
       </c>
     </row>
     <row r="99">
@@ -22542,7 +22542,7 @@
         <v>HIGH</v>
       </c>
       <c r="E99" t="str">
-        <v>0.144s</v>
+        <v>0.103s</v>
       </c>
     </row>
     <row r="100">
@@ -22559,7 +22559,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E100" t="str">
-        <v>0.065s</v>
+        <v>0.139s</v>
       </c>
     </row>
     <row r="101">
@@ -22576,7 +22576,7 @@
         <v>LOW</v>
       </c>
       <c r="E101" t="str">
-        <v>0.080s</v>
+        <v>0.081s</v>
       </c>
     </row>
     <row r="102">
@@ -22593,7 +22593,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E102" t="str">
-        <v>0.148s</v>
+        <v>0.054s</v>
       </c>
     </row>
     <row r="103">
@@ -22610,7 +22610,7 @@
         <v>LOW</v>
       </c>
       <c r="E103" t="str">
-        <v>0.114s</v>
+        <v>0.120s</v>
       </c>
     </row>
     <row r="104">
@@ -22627,7 +22627,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E104" t="str">
-        <v>0.155s</v>
+        <v>0.071s</v>
       </c>
     </row>
     <row r="105">
@@ -22644,7 +22644,7 @@
         <v>HIGH</v>
       </c>
       <c r="E105" t="str">
-        <v>0.096s</v>
+        <v>0.102s</v>
       </c>
     </row>
     <row r="106">
@@ -22661,7 +22661,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E106" t="str">
-        <v>0.044s</v>
+        <v>0.086s</v>
       </c>
     </row>
     <row r="107">
@@ -22678,7 +22678,7 @@
         <v>LOW</v>
       </c>
       <c r="E107" t="str">
-        <v>0.151s</v>
+        <v>0.078s</v>
       </c>
     </row>
     <row r="108">
@@ -22695,7 +22695,7 @@
         <v>HIGH</v>
       </c>
       <c r="E108" t="str">
-        <v>0.125s</v>
+        <v>0.137s</v>
       </c>
     </row>
     <row r="109">
@@ -22712,7 +22712,7 @@
         <v>LOW</v>
       </c>
       <c r="E109" t="str">
-        <v>0.070s</v>
+        <v>0.062s</v>
       </c>
     </row>
     <row r="110">
@@ -22729,7 +22729,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E110" t="str">
-        <v>0.152s</v>
+        <v>0.055s</v>
       </c>
     </row>
     <row r="111">
@@ -22746,7 +22746,7 @@
         <v>LOW</v>
       </c>
       <c r="E111" t="str">
-        <v>0.121s</v>
+        <v>0.109s</v>
       </c>
     </row>
     <row r="112">
@@ -22763,7 +22763,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E112" t="str">
-        <v>0.086s</v>
+        <v>0.097s</v>
       </c>
     </row>
     <row r="113">
@@ -22780,7 +22780,7 @@
         <v>HIGH</v>
       </c>
       <c r="E113" t="str">
-        <v>0.080s</v>
+        <v>0.108s</v>
       </c>
     </row>
     <row r="114">
@@ -22797,7 +22797,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E114" t="str">
-        <v>0.072s</v>
+        <v>0.111s</v>
       </c>
     </row>
     <row r="115">
@@ -22814,7 +22814,7 @@
         <v>LOW</v>
       </c>
       <c r="E115" t="str">
-        <v>0.086s</v>
+        <v>0.150s</v>
       </c>
     </row>
     <row r="116">
@@ -22831,7 +22831,7 @@
         <v>HIGH</v>
       </c>
       <c r="E116" t="str">
-        <v>0.143s</v>
+        <v>0.136s</v>
       </c>
     </row>
     <row r="117">
@@ -22848,7 +22848,7 @@
         <v>LOW</v>
       </c>
       <c r="E117" t="str">
-        <v>0.155s</v>
+        <v>0.149s</v>
       </c>
     </row>
     <row r="118">
@@ -22865,7 +22865,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E118" t="str">
-        <v>0.108s</v>
+        <v>0.076s</v>
       </c>
     </row>
     <row r="119">
@@ -22882,7 +22882,7 @@
         <v>HIGH</v>
       </c>
       <c r="E119" t="str">
-        <v>0.115s</v>
+        <v>0.065s</v>
       </c>
     </row>
     <row r="120">
@@ -22899,7 +22899,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E120" t="str">
-        <v>0.044s</v>
+        <v>0.139s</v>
       </c>
     </row>
     <row r="121">
@@ -22916,7 +22916,7 @@
         <v>LOW</v>
       </c>
       <c r="E121" t="str">
-        <v>0.114s</v>
+        <v>0.147s</v>
       </c>
     </row>
     <row r="122">
@@ -22933,7 +22933,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E122" t="str">
-        <v>0.093s</v>
+        <v>0.121s</v>
       </c>
     </row>
     <row r="123">
@@ -22950,7 +22950,7 @@
         <v>LOW</v>
       </c>
       <c r="E123" t="str">
-        <v>0.130s</v>
+        <v>0.058s</v>
       </c>
     </row>
     <row r="124">
@@ -22967,7 +22967,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E124" t="str">
-        <v>0.113s</v>
+        <v>0.069s</v>
       </c>
     </row>
     <row r="125">
@@ -22984,7 +22984,7 @@
         <v>HIGH</v>
       </c>
       <c r="E125" t="str">
-        <v>0.115s</v>
+        <v>0.040s</v>
       </c>
     </row>
     <row r="126">
@@ -23001,7 +23001,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E126" t="str">
-        <v>0.080s</v>
+        <v>0.138s</v>
       </c>
     </row>
     <row r="127">
@@ -23018,7 +23018,7 @@
         <v>LOW</v>
       </c>
       <c r="E127" t="str">
-        <v>0.136s</v>
+        <v>0.132s</v>
       </c>
     </row>
     <row r="128">
@@ -23035,7 +23035,7 @@
         <v>HIGH</v>
       </c>
       <c r="E128" t="str">
-        <v>0.157s</v>
+        <v>0.092s</v>
       </c>
     </row>
     <row r="129">
@@ -23052,7 +23052,7 @@
         <v>LOW</v>
       </c>
       <c r="E129" t="str">
-        <v>0.072s</v>
+        <v>0.135s</v>
       </c>
     </row>
     <row r="130">
@@ -23069,7 +23069,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E130" t="str">
-        <v>0.121s</v>
+        <v>0.090s</v>
       </c>
     </row>
     <row r="131">
@@ -23103,7 +23103,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E132" t="str">
-        <v>0.149s</v>
+        <v>0.082s</v>
       </c>
     </row>
     <row r="133">
@@ -23120,7 +23120,7 @@
         <v>LOW</v>
       </c>
       <c r="E133" t="str">
-        <v>0.093s</v>
+        <v>0.114s</v>
       </c>
     </row>
     <row r="134">
@@ -23137,7 +23137,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E134" t="str">
-        <v>0.043s</v>
+        <v>0.065s</v>
       </c>
     </row>
     <row r="135">
@@ -23154,7 +23154,7 @@
         <v>LOW</v>
       </c>
       <c r="E135" t="str">
-        <v>0.077s</v>
+        <v>0.055s</v>
       </c>
     </row>
     <row r="136">
@@ -23171,7 +23171,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E136" t="str">
-        <v>0.056s</v>
+        <v>0.100s</v>
       </c>
     </row>
     <row r="137">
@@ -23188,7 +23188,7 @@
         <v>HIGH</v>
       </c>
       <c r="E137" t="str">
-        <v>0.050s</v>
+        <v>0.127s</v>
       </c>
     </row>
     <row r="138">
@@ -23205,7 +23205,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E138" t="str">
-        <v>0.153s</v>
+        <v>0.139s</v>
       </c>
     </row>
     <row r="139">
@@ -23222,7 +23222,7 @@
         <v>LOW</v>
       </c>
       <c r="E139" t="str">
-        <v>0.054s</v>
+        <v>0.052s</v>
       </c>
     </row>
     <row r="140">
@@ -23239,7 +23239,7 @@
         <v>HIGH</v>
       </c>
       <c r="E140" t="str">
-        <v>0.153s</v>
+        <v>0.148s</v>
       </c>
     </row>
     <row r="141">
@@ -23256,7 +23256,7 @@
         <v>LOW</v>
       </c>
       <c r="E141" t="str">
-        <v>0.097s</v>
+        <v>0.063s</v>
       </c>
     </row>
     <row r="142">
@@ -23273,7 +23273,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E142" t="str">
-        <v>0.117s</v>
+        <v>0.157s</v>
       </c>
     </row>
     <row r="143">
@@ -23290,7 +23290,7 @@
         <v>HIGH</v>
       </c>
       <c r="E143" t="str">
-        <v>0.099s</v>
+        <v>0.123s</v>
       </c>
     </row>
     <row r="144">
@@ -23307,7 +23307,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E144" t="str">
-        <v>0.085s</v>
+        <v>0.126s</v>
       </c>
     </row>
     <row r="145">
@@ -23324,7 +23324,7 @@
         <v>LOW</v>
       </c>
       <c r="E145" t="str">
-        <v>0.114s</v>
+        <v>0.089s</v>
       </c>
     </row>
     <row r="146">
@@ -23341,7 +23341,7 @@
         <v>HIGH</v>
       </c>
       <c r="E146" t="str">
-        <v>0.151s</v>
+        <v>0.123s</v>
       </c>
     </row>
     <row r="147">
@@ -23358,7 +23358,7 @@
         <v>LOW</v>
       </c>
       <c r="E147" t="str">
-        <v>0.067s</v>
+        <v>0.058s</v>
       </c>
     </row>
     <row r="148">
@@ -23375,7 +23375,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E148" t="str">
-        <v>0.066s</v>
+        <v>0.109s</v>
       </c>
     </row>
     <row r="149">
@@ -23392,7 +23392,7 @@
         <v>HIGH</v>
       </c>
       <c r="E149" t="str">
-        <v>0.111s</v>
+        <v>0.152s</v>
       </c>
     </row>
     <row r="150">
@@ -23409,7 +23409,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E150" t="str">
-        <v>0.133s</v>
+        <v>0.130s</v>
       </c>
     </row>
     <row r="151">
@@ -23426,7 +23426,7 @@
         <v>LOW</v>
       </c>
       <c r="E151" t="str">
-        <v>0.093s</v>
+        <v>0.142s</v>
       </c>
     </row>
     <row r="152">
@@ -23443,7 +23443,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E152" t="str">
-        <v>0.101s</v>
+        <v>0.102s</v>
       </c>
     </row>
     <row r="153">
@@ -23460,7 +23460,7 @@
         <v>LOW</v>
       </c>
       <c r="E153" t="str">
-        <v>0.105s</v>
+        <v>0.159s</v>
       </c>
     </row>
     <row r="154">
@@ -23477,7 +23477,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E154" t="str">
-        <v>0.048s</v>
+        <v>0.044s</v>
       </c>
     </row>
     <row r="155">
@@ -23494,7 +23494,7 @@
         <v>HIGH</v>
       </c>
       <c r="E155" t="str">
-        <v>0.125s</v>
+        <v>0.108s</v>
       </c>
     </row>
     <row r="156">
@@ -23511,7 +23511,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E156" t="str">
-        <v>0.043s</v>
+        <v>0.109s</v>
       </c>
     </row>
     <row r="157">
@@ -23528,7 +23528,7 @@
         <v>LOW</v>
       </c>
       <c r="E157" t="str">
-        <v>0.138s</v>
+        <v>0.076s</v>
       </c>
     </row>
     <row r="158">
@@ -23545,7 +23545,7 @@
         <v>HIGH</v>
       </c>
       <c r="E158" t="str">
-        <v>0.103s</v>
+        <v>0.134s</v>
       </c>
     </row>
     <row r="159">
@@ -23562,7 +23562,7 @@
         <v>LOW</v>
       </c>
       <c r="E159" t="str">
-        <v>0.132s</v>
+        <v>0.067s</v>
       </c>
     </row>
     <row r="160">
@@ -23579,7 +23579,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E160" t="str">
-        <v>0.148s</v>
+        <v>0.113s</v>
       </c>
     </row>
     <row r="161">
@@ -23596,7 +23596,7 @@
         <v>LOW</v>
       </c>
       <c r="E161" t="str">
-        <v>0.113s</v>
+        <v>0.099s</v>
       </c>
     </row>
     <row r="162">
@@ -23613,7 +23613,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E162" t="str">
-        <v>0.104s</v>
+        <v>0.119s</v>
       </c>
     </row>
     <row r="163">
@@ -23630,7 +23630,7 @@
         <v>HIGH</v>
       </c>
       <c r="E163" t="str">
-        <v>0.124s</v>
+        <v>0.053s</v>
       </c>
     </row>
     <row r="164">
@@ -23647,7 +23647,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E164" t="str">
-        <v>0.066s</v>
+        <v>0.103s</v>
       </c>
     </row>
     <row r="165">
@@ -23664,7 +23664,7 @@
         <v>LOW</v>
       </c>
       <c r="E165" t="str">
-        <v>0.130s</v>
+        <v>0.085s</v>
       </c>
     </row>
     <row r="166">
@@ -23681,7 +23681,7 @@
         <v>HIGH</v>
       </c>
       <c r="E166" t="str">
-        <v>0.051s</v>
+        <v>0.129s</v>
       </c>
     </row>
     <row r="167">
@@ -23698,7 +23698,7 @@
         <v>LOW</v>
       </c>
       <c r="E167" t="str">
-        <v>0.126s</v>
+        <v>0.082s</v>
       </c>
     </row>
     <row r="168">
@@ -23715,7 +23715,7 @@
         <v>HIGH</v>
       </c>
       <c r="E168" t="str">
-        <v>0.066s</v>
+        <v>0.048s</v>
       </c>
     </row>
     <row r="169">
@@ -23732,7 +23732,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E169" t="str">
-        <v>0.134s</v>
+        <v>0.058s</v>
       </c>
     </row>
     <row r="170">
@@ -23749,7 +23749,7 @@
         <v>LOW</v>
       </c>
       <c r="E170" t="str">
-        <v>0.098s</v>
+        <v>0.124s</v>
       </c>
     </row>
     <row r="171">
@@ -23766,7 +23766,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E171" t="str">
-        <v>0.081s</v>
+        <v>0.152s</v>
       </c>
     </row>
     <row r="172">
@@ -23783,7 +23783,7 @@
         <v>LOW</v>
       </c>
       <c r="E172" t="str">
-        <v>0.137s</v>
+        <v>0.128s</v>
       </c>
     </row>
     <row r="173">
@@ -23800,7 +23800,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E173" t="str">
-        <v>0.146s</v>
+        <v>0.125s</v>
       </c>
     </row>
     <row r="174">
@@ -23817,7 +23817,7 @@
         <v>HIGH</v>
       </c>
       <c r="E174" t="str">
-        <v>0.117s</v>
+        <v>0.146s</v>
       </c>
     </row>
     <row r="175">
@@ -23834,7 +23834,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E175" t="str">
-        <v>0.117s</v>
+        <v>0.125s</v>
       </c>
     </row>
     <row r="176">
@@ -23851,7 +23851,7 @@
         <v>LOW</v>
       </c>
       <c r="E176" t="str">
-        <v>0.056s</v>
+        <v>0.122s</v>
       </c>
     </row>
     <row r="177">
@@ -23868,7 +23868,7 @@
         <v>HIGH</v>
       </c>
       <c r="E177" t="str">
-        <v>0.097s</v>
+        <v>0.159s</v>
       </c>
     </row>
     <row r="178">
@@ -23885,7 +23885,7 @@
         <v>LOW</v>
       </c>
       <c r="E178" t="str">
-        <v>0.117s</v>
+        <v>0.053s</v>
       </c>
     </row>
     <row r="179">
@@ -23902,7 +23902,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E179" t="str">
-        <v>0.042s</v>
+        <v>0.113s</v>
       </c>
     </row>
     <row r="180">
@@ -23919,7 +23919,7 @@
         <v>HIGH</v>
       </c>
       <c r="E180" t="str">
-        <v>0.051s</v>
+        <v>0.111s</v>
       </c>
     </row>
     <row r="181">
@@ -23936,7 +23936,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E181" t="str">
-        <v>0.135s</v>
+        <v>0.117s</v>
       </c>
     </row>
     <row r="182">
@@ -23953,7 +23953,7 @@
         <v>LOW</v>
       </c>
       <c r="E182" t="str">
-        <v>0.113s</v>
+        <v>0.078s</v>
       </c>
     </row>
     <row r="183">
@@ -23970,7 +23970,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E183" t="str">
-        <v>0.057s</v>
+        <v>0.090s</v>
       </c>
     </row>
     <row r="184">
@@ -23987,7 +23987,7 @@
         <v>LOW</v>
       </c>
       <c r="E184" t="str">
-        <v>0.080s</v>
+        <v>0.158s</v>
       </c>
     </row>
     <row r="185">
@@ -24004,7 +24004,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E185" t="str">
-        <v>0.131s</v>
+        <v>0.141s</v>
       </c>
     </row>
     <row r="186">
@@ -24021,7 +24021,7 @@
         <v>HIGH</v>
       </c>
       <c r="E186" t="str">
-        <v>0.159s</v>
+        <v>0.139s</v>
       </c>
     </row>
     <row r="187">
@@ -24038,7 +24038,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E187" t="str">
-        <v>0.143s</v>
+        <v>0.092s</v>
       </c>
     </row>
     <row r="188">
@@ -24055,7 +24055,7 @@
         <v>LOW</v>
       </c>
       <c r="E188" t="str">
-        <v>0.117s</v>
+        <v>0.044s</v>
       </c>
     </row>
     <row r="189">
@@ -24072,7 +24072,7 @@
         <v>HIGH</v>
       </c>
       <c r="E189" t="str">
-        <v>0.149s</v>
+        <v>0.135s</v>
       </c>
     </row>
     <row r="190">
@@ -24089,7 +24089,7 @@
         <v>LOW</v>
       </c>
       <c r="E190" t="str">
-        <v>0.147s</v>
+        <v>0.064s</v>
       </c>
     </row>
     <row r="191">
@@ -24106,7 +24106,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E191" t="str">
-        <v>0.062s</v>
+        <v>0.141s</v>
       </c>
     </row>
     <row r="192">
@@ -24123,7 +24123,7 @@
         <v>HIGH</v>
       </c>
       <c r="E192" t="str">
-        <v>0.074s</v>
+        <v>0.051s</v>
       </c>
     </row>
     <row r="193">
@@ -24140,7 +24140,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E193" t="str">
-        <v>0.103s</v>
+        <v>0.156s</v>
       </c>
     </row>
     <row r="194">
@@ -24157,7 +24157,7 @@
         <v>LOW</v>
       </c>
       <c r="E194" t="str">
-        <v>0.147s</v>
+        <v>0.158s</v>
       </c>
     </row>
     <row r="195">
@@ -24174,7 +24174,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E195" t="str">
-        <v>0.136s</v>
+        <v>0.143s</v>
       </c>
     </row>
     <row r="196">
@@ -24191,7 +24191,7 @@
         <v>LOW</v>
       </c>
       <c r="E196" t="str">
-        <v>0.098s</v>
+        <v>0.120s</v>
       </c>
     </row>
     <row r="197">
@@ -24208,7 +24208,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E197" t="str">
-        <v>0.085s</v>
+        <v>0.048s</v>
       </c>
     </row>
     <row r="198">
@@ -24225,7 +24225,7 @@
         <v>HIGH</v>
       </c>
       <c r="E198" t="str">
-        <v>0.123s</v>
+        <v>0.102s</v>
       </c>
     </row>
     <row r="199">
@@ -24242,7 +24242,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E199" t="str">
-        <v>0.122s</v>
+        <v>0.106s</v>
       </c>
     </row>
     <row r="200">
@@ -24259,7 +24259,7 @@
         <v>LOW</v>
       </c>
       <c r="E200" t="str">
-        <v>0.058s</v>
+        <v>0.077s</v>
       </c>
     </row>
     <row r="201">
@@ -24276,7 +24276,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E201" t="str">
-        <v>0.065s</v>
+        <v>0.107s</v>
       </c>
     </row>
     <row r="202">
@@ -24293,7 +24293,7 @@
         <v>HIGH</v>
       </c>
       <c r="E202" t="str">
-        <v>0.066s</v>
+        <v>0.125s</v>
       </c>
     </row>
     <row r="203">
@@ -24310,7 +24310,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E203" t="str">
-        <v>0.055s</v>
+        <v>0.126s</v>
       </c>
     </row>
     <row r="204">
@@ -24327,7 +24327,7 @@
         <v>LOW</v>
       </c>
       <c r="E204" t="str">
-        <v>0.150s</v>
+        <v>0.078s</v>
       </c>
     </row>
     <row r="205">
@@ -24344,7 +24344,7 @@
         <v>HIGH</v>
       </c>
       <c r="E205" t="str">
-        <v>0.042s</v>
+        <v>0.155s</v>
       </c>
     </row>
     <row r="206">
@@ -24361,7 +24361,7 @@
         <v>LOW</v>
       </c>
       <c r="E206" t="str">
-        <v>0.112s</v>
+        <v>0.081s</v>
       </c>
     </row>
     <row r="207">
@@ -24378,7 +24378,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E207" t="str">
-        <v>0.090s</v>
+        <v>0.051s</v>
       </c>
     </row>
     <row r="208">
@@ -24395,7 +24395,7 @@
         <v>HIGH</v>
       </c>
       <c r="E208" t="str">
-        <v>0.158s</v>
+        <v>0.134s</v>
       </c>
     </row>
     <row r="209">
@@ -24412,7 +24412,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E209" t="str">
-        <v>0.122s</v>
+        <v>0.144s</v>
       </c>
     </row>
     <row r="210">
@@ -24429,7 +24429,7 @@
         <v>LOW</v>
       </c>
       <c r="E210" t="str">
-        <v>0.066s</v>
+        <v>0.077s</v>
       </c>
     </row>
     <row r="211">
@@ -24446,7 +24446,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E211" t="str">
-        <v>0.149s</v>
+        <v>0.117s</v>
       </c>
     </row>
     <row r="212">
@@ -24463,7 +24463,7 @@
         <v>LOW</v>
       </c>
       <c r="E212" t="str">
-        <v>0.111s</v>
+        <v>0.145s</v>
       </c>
     </row>
     <row r="213">
@@ -24480,7 +24480,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E213" t="str">
-        <v>0.052s</v>
+        <v>0.108s</v>
       </c>
     </row>
     <row r="214">
@@ -24497,7 +24497,7 @@
         <v>HIGH</v>
       </c>
       <c r="E214" t="str">
-        <v>0.062s</v>
+        <v>0.086s</v>
       </c>
     </row>
     <row r="215">
@@ -24514,7 +24514,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E215" t="str">
-        <v>0.128s</v>
+        <v>0.065s</v>
       </c>
     </row>
     <row r="216">
@@ -24531,7 +24531,7 @@
         <v>LOW</v>
       </c>
       <c r="E216" t="str">
-        <v>0.130s</v>
+        <v>0.149s</v>
       </c>
     </row>
     <row r="217">
@@ -24548,7 +24548,7 @@
         <v>HIGH</v>
       </c>
       <c r="E217" t="str">
-        <v>0.063s</v>
+        <v>0.082s</v>
       </c>
     </row>
     <row r="218">
@@ -24565,7 +24565,7 @@
         <v>LOW</v>
       </c>
       <c r="E218" t="str">
-        <v>0.127s</v>
+        <v>0.088s</v>
       </c>
     </row>
     <row r="219">
@@ -24582,7 +24582,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E219" t="str">
-        <v>0.102s</v>
+        <v>0.050s</v>
       </c>
     </row>
     <row r="220">
@@ -24599,7 +24599,7 @@
         <v>HIGH</v>
       </c>
       <c r="E220" t="str">
-        <v>0.113s</v>
+        <v>0.089s</v>
       </c>
     </row>
     <row r="221">
@@ -24616,7 +24616,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E221" t="str">
-        <v>0.132s</v>
+        <v>0.109s</v>
       </c>
     </row>
     <row r="222">
@@ -24633,7 +24633,7 @@
         <v>LOW</v>
       </c>
       <c r="E222" t="str">
-        <v>0.135s</v>
+        <v>0.068s</v>
       </c>
     </row>
     <row r="223">
@@ -24650,7 +24650,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E223" t="str">
-        <v>0.081s</v>
+        <v>0.117s</v>
       </c>
     </row>
     <row r="224">
@@ -24667,7 +24667,7 @@
         <v>LOW</v>
       </c>
       <c r="E224" t="str">
-        <v>0.124s</v>
+        <v>0.112s</v>
       </c>
     </row>
     <row r="225">
@@ -24684,7 +24684,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E225" t="str">
-        <v>0.071s</v>
+        <v>0.074s</v>
       </c>
     </row>
     <row r="226">
@@ -24701,7 +24701,7 @@
         <v>HIGH</v>
       </c>
       <c r="E226" t="str">
-        <v>0.063s</v>
+        <v>0.151s</v>
       </c>
     </row>
     <row r="227">
@@ -24718,7 +24718,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E227" t="str">
-        <v>0.133s</v>
+        <v>0.100s</v>
       </c>
     </row>
     <row r="228">
@@ -24735,7 +24735,7 @@
         <v>LOW</v>
       </c>
       <c r="E228" t="str">
-        <v>0.123s</v>
+        <v>0.047s</v>
       </c>
     </row>
     <row r="229">
@@ -24752,7 +24752,7 @@
         <v>HIGH</v>
       </c>
       <c r="E229" t="str">
-        <v>0.063s</v>
+        <v>0.067s</v>
       </c>
     </row>
     <row r="230">
@@ -24769,7 +24769,7 @@
         <v>LOW</v>
       </c>
       <c r="E230" t="str">
-        <v>0.051s</v>
+        <v>0.107s</v>
       </c>
     </row>
     <row r="231">
@@ -24786,7 +24786,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E231" t="str">
-        <v>0.070s</v>
+        <v>0.071s</v>
       </c>
     </row>
     <row r="232">
@@ -24803,7 +24803,7 @@
         <v>HIGH</v>
       </c>
       <c r="E232" t="str">
-        <v>0.079s</v>
+        <v>0.101s</v>
       </c>
     </row>
     <row r="233">
@@ -24820,7 +24820,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E233" t="str">
-        <v>0.148s</v>
+        <v>0.137s</v>
       </c>
     </row>
     <row r="234">
@@ -24837,7 +24837,7 @@
         <v>LOW</v>
       </c>
       <c r="E234" t="str">
-        <v>0.140s</v>
+        <v>0.079s</v>
       </c>
     </row>
     <row r="235">
@@ -24854,7 +24854,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E235" t="str">
-        <v>0.104s</v>
+        <v>0.096s</v>
       </c>
     </row>
     <row r="236">
@@ -24871,7 +24871,7 @@
         <v>LOW</v>
       </c>
       <c r="E236" t="str">
-        <v>0.145s</v>
+        <v>0.135s</v>
       </c>
     </row>
     <row r="237">
@@ -24888,7 +24888,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E237" t="str">
-        <v>0.106s</v>
+        <v>0.100s</v>
       </c>
     </row>
     <row r="238">
@@ -24905,7 +24905,7 @@
         <v>HIGH</v>
       </c>
       <c r="E238" t="str">
-        <v>0.126s</v>
+        <v>0.146s</v>
       </c>
     </row>
     <row r="239">
@@ -24922,7 +24922,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E239" t="str">
-        <v>0.110s</v>
+        <v>0.042s</v>
       </c>
     </row>
     <row r="240">
@@ -24939,7 +24939,7 @@
         <v>LOW</v>
       </c>
       <c r="E240" t="str">
-        <v>0.067s</v>
+        <v>0.063s</v>
       </c>
     </row>
     <row r="241">
@@ -24956,7 +24956,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E241" t="str">
-        <v>0.054s</v>
+        <v>0.152s</v>
       </c>
     </row>
     <row r="242">
@@ -24973,7 +24973,7 @@
         <v>HIGH</v>
       </c>
       <c r="E242" t="str">
-        <v>0.058s</v>
+        <v>0.147s</v>
       </c>
     </row>
     <row r="243">
@@ -24990,7 +24990,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E243" t="str">
-        <v>0.094s</v>
+        <v>0.040s</v>
       </c>
     </row>
     <row r="244">
@@ -25007,7 +25007,7 @@
         <v>LOW</v>
       </c>
       <c r="E244" t="str">
-        <v>0.110s</v>
+        <v>0.081s</v>
       </c>
     </row>
     <row r="245">
@@ -25024,7 +25024,7 @@
         <v>HIGH</v>
       </c>
       <c r="E245" t="str">
-        <v>0.124s</v>
+        <v>0.092s</v>
       </c>
     </row>
     <row r="246">
@@ -25041,7 +25041,7 @@
         <v>LOW</v>
       </c>
       <c r="E246" t="str">
-        <v>0.151s</v>
+        <v>0.143s</v>
       </c>
     </row>
     <row r="247">
@@ -25058,7 +25058,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E247" t="str">
-        <v>0.118s</v>
+        <v>0.064s</v>
       </c>
     </row>
     <row r="248">
@@ -25075,7 +25075,7 @@
         <v>HIGH</v>
       </c>
       <c r="E248" t="str">
-        <v>0.044s</v>
+        <v>0.075s</v>
       </c>
     </row>
     <row r="249">
@@ -25092,7 +25092,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E249" t="str">
-        <v>0.041s</v>
+        <v>0.138s</v>
       </c>
     </row>
     <row r="250">
@@ -25109,7 +25109,7 @@
         <v>LOW</v>
       </c>
       <c r="E250" t="str">
-        <v>0.143s</v>
+        <v>0.053s</v>
       </c>
     </row>
     <row r="251">
@@ -25126,7 +25126,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E251" t="str">
-        <v>0.070s</v>
+        <v>0.072s</v>
       </c>
     </row>
     <row r="252">
@@ -25143,7 +25143,7 @@
         <v>LOW</v>
       </c>
       <c r="E252" t="str">
-        <v>0.114s</v>
+        <v>0.137s</v>
       </c>
     </row>
     <row r="253">
@@ -25160,7 +25160,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E253" t="str">
-        <v>0.049s</v>
+        <v>0.071s</v>
       </c>
     </row>
     <row r="254">
@@ -25177,7 +25177,7 @@
         <v>HIGH</v>
       </c>
       <c r="E254" t="str">
-        <v>0.108s</v>
+        <v>0.148s</v>
       </c>
     </row>
     <row r="255">
@@ -25194,7 +25194,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E255" t="str">
-        <v>0.155s</v>
+        <v>0.147s</v>
       </c>
     </row>
     <row r="256">
@@ -25211,7 +25211,7 @@
         <v>LOW</v>
       </c>
       <c r="E256" t="str">
-        <v>0.081s</v>
+        <v>0.103s</v>
       </c>
     </row>
     <row r="257">
@@ -25228,7 +25228,7 @@
         <v>HIGH</v>
       </c>
       <c r="E257" t="str">
-        <v>0.123s</v>
+        <v>0.096s</v>
       </c>
     </row>
     <row r="258">
@@ -25245,7 +25245,7 @@
         <v>LOW</v>
       </c>
       <c r="E258" t="str">
-        <v>0.097s</v>
+        <v>0.057s</v>
       </c>
     </row>
     <row r="259">
@@ -25279,7 +25279,7 @@
         <v>LOW</v>
       </c>
       <c r="E260" t="str">
-        <v>0.049s</v>
+        <v>0.051s</v>
       </c>
     </row>
     <row r="261">
@@ -25296,7 +25296,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E261" t="str">
-        <v>0.072s</v>
+        <v>0.150s</v>
       </c>
     </row>
     <row r="262">
@@ -25313,7 +25313,7 @@
         <v>HIGH</v>
       </c>
       <c r="E262" t="str">
-        <v>0.086s</v>
+        <v>0.041s</v>
       </c>
     </row>
     <row r="263">
@@ -25330,7 +25330,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E263" t="str">
-        <v>0.111s</v>
+        <v>0.045s</v>
       </c>
     </row>
     <row r="264">
@@ -25347,7 +25347,7 @@
         <v>LOW</v>
       </c>
       <c r="E264" t="str">
-        <v>0.075s</v>
+        <v>0.125s</v>
       </c>
     </row>
     <row r="265">
@@ -25364,7 +25364,7 @@
         <v>HIGH</v>
       </c>
       <c r="E265" t="str">
-        <v>0.080s</v>
+        <v>0.148s</v>
       </c>
     </row>
     <row r="266">
@@ -25381,7 +25381,7 @@
         <v>LOW</v>
       </c>
       <c r="E266" t="str">
-        <v>0.076s</v>
+        <v>0.055s</v>
       </c>
     </row>
     <row r="267">
@@ -25398,7 +25398,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E267" t="str">
-        <v>0.070s</v>
+        <v>0.079s</v>
       </c>
     </row>
     <row r="268">
@@ -25415,7 +25415,7 @@
         <v>HIGH</v>
       </c>
       <c r="E268" t="str">
-        <v>0.049s</v>
+        <v>0.044s</v>
       </c>
     </row>
     <row r="269">
@@ -25432,7 +25432,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E269" t="str">
-        <v>0.158s</v>
+        <v>0.057s</v>
       </c>
     </row>
     <row r="270">
@@ -25449,7 +25449,7 @@
         <v>LOW</v>
       </c>
       <c r="E270" t="str">
-        <v>0.067s</v>
+        <v>0.096s</v>
       </c>
     </row>
     <row r="271">
@@ -25466,7 +25466,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E271" t="str">
-        <v>0.059s</v>
+        <v>0.040s</v>
       </c>
     </row>
     <row r="272">
@@ -25500,7 +25500,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E273" t="str">
-        <v>0.107s</v>
+        <v>0.122s</v>
       </c>
     </row>
     <row r="274">
@@ -25517,7 +25517,7 @@
         <v>HIGH</v>
       </c>
       <c r="E274" t="str">
-        <v>0.107s</v>
+        <v>0.129s</v>
       </c>
     </row>
     <row r="275">
@@ -25534,7 +25534,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E275" t="str">
-        <v>0.110s</v>
+        <v>0.067s</v>
       </c>
     </row>
     <row r="276">
@@ -25551,7 +25551,7 @@
         <v>LOW</v>
       </c>
       <c r="E276" t="str">
-        <v>0.075s</v>
+        <v>0.132s</v>
       </c>
     </row>
     <row r="277">
@@ -25568,7 +25568,7 @@
         <v>HIGH</v>
       </c>
       <c r="E277" t="str">
-        <v>0.149s</v>
+        <v>0.101s</v>
       </c>
     </row>
     <row r="278">
@@ -25585,7 +25585,7 @@
         <v>LOW</v>
       </c>
       <c r="E278" t="str">
-        <v>0.065s</v>
+        <v>0.049s</v>
       </c>
     </row>
     <row r="279">
@@ -25602,7 +25602,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E279" t="str">
-        <v>0.076s</v>
+        <v>0.091s</v>
       </c>
     </row>
     <row r="280">
@@ -25619,7 +25619,7 @@
         <v>LOW</v>
       </c>
       <c r="E280" t="str">
-        <v>0.063s</v>
+        <v>0.156s</v>
       </c>
     </row>
     <row r="281">
@@ -25636,7 +25636,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E281" t="str">
-        <v>0.099s</v>
+        <v>0.108s</v>
       </c>
     </row>
     <row r="282">
@@ -25653,7 +25653,7 @@
         <v>HIGH</v>
       </c>
       <c r="E282" t="str">
-        <v>0.049s</v>
+        <v>0.107s</v>
       </c>
     </row>
     <row r="283">
@@ -25670,7 +25670,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E283" t="str">
-        <v>0.073s</v>
+        <v>0.095s</v>
       </c>
     </row>
     <row r="284">
@@ -25687,7 +25687,7 @@
         <v>LOW</v>
       </c>
       <c r="E284" t="str">
-        <v>0.095s</v>
+        <v>0.046s</v>
       </c>
     </row>
     <row r="285">
@@ -25704,7 +25704,7 @@
         <v>HIGH</v>
       </c>
       <c r="E285" t="str">
-        <v>0.133s</v>
+        <v>0.094s</v>
       </c>
     </row>
     <row r="286">
@@ -25721,7 +25721,7 @@
         <v>LOW</v>
       </c>
       <c r="E286" t="str">
-        <v>0.087s</v>
+        <v>0.150s</v>
       </c>
     </row>
     <row r="287">
@@ -25738,7 +25738,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E287" t="str">
-        <v>0.110s</v>
+        <v>0.154s</v>
       </c>
     </row>
     <row r="288">
@@ -25755,7 +25755,7 @@
         <v>HIGH</v>
       </c>
       <c r="E288" t="str">
-        <v>0.111s</v>
+        <v>0.084s</v>
       </c>
     </row>
     <row r="289">
@@ -25772,7 +25772,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E289" t="str">
-        <v>0.110s</v>
+        <v>0.070s</v>
       </c>
     </row>
     <row r="290">
@@ -25789,7 +25789,7 @@
         <v>LOW</v>
       </c>
       <c r="E290" t="str">
-        <v>0.073s</v>
+        <v>0.070s</v>
       </c>
     </row>
     <row r="291">
@@ -25806,7 +25806,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E291" t="str">
-        <v>0.044s</v>
+        <v>0.051s</v>
       </c>
     </row>
     <row r="292">
@@ -25823,7 +25823,7 @@
         <v>LOW</v>
       </c>
       <c r="E292" t="str">
-        <v>0.060s</v>
+        <v>0.132s</v>
       </c>
     </row>
     <row r="293">
@@ -25840,7 +25840,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E293" t="str">
-        <v>0.052s</v>
+        <v>0.128s</v>
       </c>
     </row>
     <row r="294">
@@ -25857,7 +25857,7 @@
         <v>HIGH</v>
       </c>
       <c r="E294" t="str">
-        <v>0.111s</v>
+        <v>0.128s</v>
       </c>
     </row>
     <row r="295">
@@ -25874,7 +25874,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E295" t="str">
-        <v>0.104s</v>
+        <v>0.066s</v>
       </c>
     </row>
     <row r="296">
@@ -25891,7 +25891,7 @@
         <v>LOW</v>
       </c>
       <c r="E296" t="str">
-        <v>0.055s</v>
+        <v>0.095s</v>
       </c>
     </row>
     <row r="297">
@@ -25908,7 +25908,7 @@
         <v>HIGH</v>
       </c>
       <c r="E297" t="str">
-        <v>0.117s</v>
+        <v>0.135s</v>
       </c>
     </row>
     <row r="298">
@@ -25925,7 +25925,7 @@
         <v>LOW</v>
       </c>
       <c r="E298" t="str">
-        <v>0.110s</v>
+        <v>0.140s</v>
       </c>
     </row>
     <row r="299">
@@ -25942,7 +25942,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E299" t="str">
-        <v>0.106s</v>
+        <v>0.067s</v>
       </c>
     </row>
     <row r="300">
@@ -25959,7 +25959,7 @@
         <v>HIGH</v>
       </c>
       <c r="E300" t="str">
-        <v>0.058s</v>
+        <v>0.052s</v>
       </c>
     </row>
     <row r="301">
@@ -25976,7 +25976,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E301" t="str">
-        <v>0.049s</v>
+        <v>0.043s</v>
       </c>
     </row>
     <row r="302">
@@ -25993,7 +25993,7 @@
         <v>LOW</v>
       </c>
       <c r="E302" t="str">
-        <v>0.091s</v>
+        <v>0.121s</v>
       </c>
     </row>
     <row r="303">
@@ -26010,7 +26010,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E303" t="str">
-        <v>0.084s</v>
+        <v>0.090s</v>
       </c>
     </row>
     <row r="304">
@@ -26027,7 +26027,7 @@
         <v>LOW</v>
       </c>
       <c r="E304" t="str">
-        <v>0.077s</v>
+        <v>0.116s</v>
       </c>
     </row>
     <row r="305">
@@ -26044,7 +26044,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E305" t="str">
-        <v>0.137s</v>
+        <v>0.084s</v>
       </c>
     </row>
     <row r="306">
@@ -26061,7 +26061,7 @@
         <v>HIGH</v>
       </c>
       <c r="E306" t="str">
-        <v>0.105s</v>
+        <v>0.107s</v>
       </c>
     </row>
     <row r="307">
@@ -26078,7 +26078,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E307" t="str">
-        <v>0.040s</v>
+        <v>0.047s</v>
       </c>
     </row>
     <row r="308">
@@ -26095,7 +26095,7 @@
         <v>LOW</v>
       </c>
       <c r="E308" t="str">
-        <v>0.146s</v>
+        <v>0.110s</v>
       </c>
     </row>
     <row r="309">
@@ -26112,7 +26112,7 @@
         <v>HIGH</v>
       </c>
       <c r="E309" t="str">
-        <v>0.087s</v>
+        <v>0.158s</v>
       </c>
     </row>
     <row r="310">
@@ -26129,7 +26129,7 @@
         <v>LOW</v>
       </c>
       <c r="E310" t="str">
-        <v>0.068s</v>
+        <v>0.138s</v>
       </c>
     </row>
     <row r="311">
@@ -26146,7 +26146,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E311" t="str">
-        <v>0.049s</v>
+        <v>0.067s</v>
       </c>
     </row>
     <row r="312">
@@ -26163,7 +26163,7 @@
         <v>HIGH</v>
       </c>
       <c r="E312" t="str">
-        <v>0.158s</v>
+        <v>0.114s</v>
       </c>
     </row>
     <row r="313">
@@ -26180,7 +26180,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E313" t="str">
-        <v>0.126s</v>
+        <v>0.100s</v>
       </c>
     </row>
     <row r="314">
@@ -26197,7 +26197,7 @@
         <v>LOW</v>
       </c>
       <c r="E314" t="str">
-        <v>0.151s</v>
+        <v>0.085s</v>
       </c>
     </row>
     <row r="315">
@@ -26214,7 +26214,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E315" t="str">
-        <v>0.100s</v>
+        <v>0.074s</v>
       </c>
     </row>
     <row r="316">
@@ -26231,7 +26231,7 @@
         <v>LOW</v>
       </c>
       <c r="E316" t="str">
-        <v>0.096s</v>
+        <v>0.112s</v>
       </c>
     </row>
     <row r="317">
@@ -26248,7 +26248,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E317" t="str">
-        <v>0.048s</v>
+        <v>0.146s</v>
       </c>
     </row>
     <row r="318">
@@ -26265,7 +26265,7 @@
         <v>HIGH</v>
       </c>
       <c r="E318" t="str">
-        <v>0.076s</v>
+        <v>0.111s</v>
       </c>
     </row>
     <row r="319">
@@ -26282,7 +26282,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E319" t="str">
-        <v>0.158s</v>
+        <v>0.101s</v>
       </c>
     </row>
     <row r="320">
@@ -26299,7 +26299,7 @@
         <v>LOW</v>
       </c>
       <c r="E320" t="str">
-        <v>0.042s</v>
+        <v>0.095s</v>
       </c>
     </row>
     <row r="321">
@@ -26316,7 +26316,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E321" t="str">
-        <v>0.121s</v>
+        <v>0.071s</v>
       </c>
     </row>
     <row r="322">
@@ -26333,7 +26333,7 @@
         <v>HIGH</v>
       </c>
       <c r="E322" t="str">
-        <v>0.046s</v>
+        <v>0.055s</v>
       </c>
     </row>
     <row r="323">
@@ -26350,7 +26350,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E323" t="str">
-        <v>0.073s</v>
+        <v>0.128s</v>
       </c>
     </row>
     <row r="324">
@@ -26367,7 +26367,7 @@
         <v>LOW</v>
       </c>
       <c r="E324" t="str">
-        <v>0.110s</v>
+        <v>0.071s</v>
       </c>
     </row>
     <row r="325">
@@ -26384,7 +26384,7 @@
         <v>HIGH</v>
       </c>
       <c r="E325" t="str">
-        <v>0.124s</v>
+        <v>0.095s</v>
       </c>
     </row>
     <row r="326">
@@ -26401,7 +26401,7 @@
         <v>LOW</v>
       </c>
       <c r="E326" t="str">
-        <v>0.087s</v>
+        <v>0.047s</v>
       </c>
     </row>
     <row r="327">
@@ -26418,7 +26418,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E327" t="str">
-        <v>0.082s</v>
+        <v>0.090s</v>
       </c>
     </row>
     <row r="328">
@@ -26435,7 +26435,7 @@
         <v>HIGH</v>
       </c>
       <c r="E328" t="str">
-        <v>0.053s</v>
+        <v>0.113s</v>
       </c>
     </row>
     <row r="329">
@@ -26452,7 +26452,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E329" t="str">
-        <v>0.097s</v>
+        <v>0.081s</v>
       </c>
     </row>
     <row r="330">
@@ -26469,7 +26469,7 @@
         <v>LOW</v>
       </c>
       <c r="E330" t="str">
-        <v>0.090s</v>
+        <v>0.105s</v>
       </c>
     </row>
     <row r="331">
@@ -26486,7 +26486,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E331" t="str">
-        <v>0.154s</v>
+        <v>0.053s</v>
       </c>
     </row>
     <row r="332">
@@ -26503,7 +26503,7 @@
         <v>LOW</v>
       </c>
       <c r="E332" t="str">
-        <v>0.100s</v>
+        <v>0.046s</v>
       </c>
     </row>
     <row r="333">
@@ -26520,7 +26520,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E333" t="str">
-        <v>0.117s</v>
+        <v>0.074s</v>
       </c>
     </row>
     <row r="334">
@@ -26537,7 +26537,7 @@
         <v>HIGH</v>
       </c>
       <c r="E334" t="str">
-        <v>0.076s</v>
+        <v>0.125s</v>
       </c>
     </row>
     <row r="335">
@@ -26554,7 +26554,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E335" t="str">
-        <v>0.132s</v>
+        <v>0.074s</v>
       </c>
     </row>
     <row r="336">
@@ -26571,7 +26571,7 @@
         <v>LOW</v>
       </c>
       <c r="E336" t="str">
-        <v>0.151s</v>
+        <v>0.131s</v>
       </c>
     </row>
     <row r="337">
@@ -26588,7 +26588,7 @@
         <v>HIGH</v>
       </c>
       <c r="E337" t="str">
-        <v>0.140s</v>
+        <v>0.074s</v>
       </c>
     </row>
     <row r="338">
@@ -26605,7 +26605,7 @@
         <v>LOW</v>
       </c>
       <c r="E338" t="str">
-        <v>0.155s</v>
+        <v>0.141s</v>
       </c>
     </row>
     <row r="339">
@@ -26622,7 +26622,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E339" t="str">
-        <v>0.042s</v>
+        <v>0.105s</v>
       </c>
     </row>
     <row r="340">
@@ -26639,7 +26639,7 @@
         <v>LOW</v>
       </c>
       <c r="E340" t="str">
-        <v>0.117s</v>
+        <v>0.078s</v>
       </c>
     </row>
     <row r="341">
@@ -26656,7 +26656,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E341" t="str">
-        <v>0.122s</v>
+        <v>0.048s</v>
       </c>
     </row>
     <row r="342">
@@ -26673,7 +26673,7 @@
         <v>HIGH</v>
       </c>
       <c r="E342" t="str">
-        <v>0.055s</v>
+        <v>0.068s</v>
       </c>
     </row>
     <row r="343">
@@ -26690,7 +26690,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E343" t="str">
-        <v>0.065s</v>
+        <v>0.076s</v>
       </c>
     </row>
     <row r="344">
@@ -26707,7 +26707,7 @@
         <v>LOW</v>
       </c>
       <c r="E344" t="str">
-        <v>0.076s</v>
+        <v>0.073s</v>
       </c>
     </row>
     <row r="345">
@@ -26724,7 +26724,7 @@
         <v>HIGH</v>
       </c>
       <c r="E345" t="str">
-        <v>0.134s</v>
+        <v>0.119s</v>
       </c>
     </row>
     <row r="346">
@@ -26741,7 +26741,7 @@
         <v>LOW</v>
       </c>
       <c r="E346" t="str">
-        <v>0.070s</v>
+        <v>0.131s</v>
       </c>
     </row>
     <row r="347">
@@ -26758,7 +26758,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E347" t="str">
-        <v>0.071s</v>
+        <v>0.150s</v>
       </c>
     </row>
     <row r="348">
@@ -26775,7 +26775,7 @@
         <v>HIGH</v>
       </c>
       <c r="E348" t="str">
-        <v>0.044s</v>
+        <v>0.108s</v>
       </c>
     </row>
     <row r="349">
@@ -26792,7 +26792,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E349" t="str">
-        <v>0.129s</v>
+        <v>0.120s</v>
       </c>
     </row>
     <row r="350">
@@ -26809,7 +26809,7 @@
         <v>LOW</v>
       </c>
       <c r="E350" t="str">
-        <v>0.083s</v>
+        <v>0.053s</v>
       </c>
     </row>
     <row r="351">
@@ -26826,7 +26826,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E351" t="str">
-        <v>0.099s</v>
+        <v>0.119s</v>
       </c>
     </row>
     <row r="352">
@@ -26843,7 +26843,7 @@
         <v>LOW</v>
       </c>
       <c r="E352" t="str">
-        <v>0.058s</v>
+        <v>0.150s</v>
       </c>
     </row>
     <row r="353">
@@ -26860,7 +26860,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E353" t="str">
-        <v>0.077s</v>
+        <v>0.072s</v>
       </c>
     </row>
     <row r="354">
@@ -26877,7 +26877,7 @@
         <v>HIGH</v>
       </c>
       <c r="E354" t="str">
-        <v>0.056s</v>
+        <v>0.085s</v>
       </c>
     </row>
     <row r="355">
@@ -26894,7 +26894,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E355" t="str">
-        <v>0.109s</v>
+        <v>0.145s</v>
       </c>
     </row>
     <row r="356">
@@ -26911,7 +26911,7 @@
         <v>LOW</v>
       </c>
       <c r="E356" t="str">
-        <v>0.148s</v>
+        <v>0.124s</v>
       </c>
     </row>
     <row r="357">
@@ -26928,7 +26928,7 @@
         <v>HIGH</v>
       </c>
       <c r="E357" t="str">
-        <v>0.040s</v>
+        <v>0.082s</v>
       </c>
     </row>
     <row r="358">
@@ -26945,7 +26945,7 @@
         <v>LOW</v>
       </c>
       <c r="E358" t="str">
-        <v>0.119s</v>
+        <v>0.090s</v>
       </c>
     </row>
     <row r="359">
@@ -26962,7 +26962,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E359" t="str">
-        <v>0.040s</v>
+        <v>0.103s</v>
       </c>
     </row>
     <row r="360">
@@ -26979,7 +26979,7 @@
         <v>LOW</v>
       </c>
       <c r="E360" t="str">
-        <v>0.134s</v>
+        <v>0.047s</v>
       </c>
     </row>
     <row r="361">
@@ -26996,7 +26996,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E361" t="str">
-        <v>0.106s</v>
+        <v>0.098s</v>
       </c>
     </row>
     <row r="362">
@@ -27013,7 +27013,7 @@
         <v>HIGH</v>
       </c>
       <c r="E362" t="str">
-        <v>0.091s</v>
+        <v>0.153s</v>
       </c>
     </row>
     <row r="363">
@@ -27030,7 +27030,7 @@
         <v>LOW</v>
       </c>
       <c r="E363" t="str">
-        <v>0.131s</v>
+        <v>0.065s</v>
       </c>
     </row>
     <row r="364">
@@ -27047,7 +27047,7 @@
         <v>HIGH</v>
       </c>
       <c r="E364" t="str">
-        <v>0.063s</v>
+        <v>0.098s</v>
       </c>
     </row>
     <row r="365">
@@ -27064,7 +27064,7 @@
         <v>LOW</v>
       </c>
       <c r="E365" t="str">
-        <v>0.146s</v>
+        <v>0.134s</v>
       </c>
     </row>
     <row r="366">
@@ -27081,7 +27081,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E366" t="str">
-        <v>0.154s</v>
+        <v>0.065s</v>
       </c>
     </row>
     <row r="367">
@@ -27098,7 +27098,7 @@
         <v>HIGH</v>
       </c>
       <c r="E367" t="str">
-        <v>0.083s</v>
+        <v>0.050s</v>
       </c>
     </row>
     <row r="368">
@@ -27115,7 +27115,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E368" t="str">
-        <v>0.135s</v>
+        <v>0.047s</v>
       </c>
     </row>
     <row r="369">
@@ -27132,7 +27132,7 @@
         <v>LOW</v>
       </c>
       <c r="E369" t="str">
-        <v>0.050s</v>
+        <v>0.097s</v>
       </c>
     </row>
     <row r="370">
@@ -27149,7 +27149,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E370" t="str">
-        <v>0.135s</v>
+        <v>0.091s</v>
       </c>
     </row>
     <row r="371">
@@ -27166,7 +27166,7 @@
         <v>LOW</v>
       </c>
       <c r="E371" t="str">
-        <v>0.128s</v>
+        <v>0.130s</v>
       </c>
     </row>
     <row r="372">
@@ -27183,7 +27183,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E372" t="str">
-        <v>0.141s</v>
+        <v>0.068s</v>
       </c>
     </row>
     <row r="373">
@@ -27200,7 +27200,7 @@
         <v>HIGH</v>
       </c>
       <c r="E373" t="str">
-        <v>0.110s</v>
+        <v>0.147s</v>
       </c>
     </row>
     <row r="374">
@@ -27217,7 +27217,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E374" t="str">
-        <v>0.047s</v>
+        <v>0.117s</v>
       </c>
     </row>
     <row r="375">
@@ -27234,7 +27234,7 @@
         <v>LOW</v>
       </c>
       <c r="E375" t="str">
-        <v>0.123s</v>
+        <v>0.104s</v>
       </c>
     </row>
     <row r="376">
@@ -27251,7 +27251,7 @@
         <v>HIGH</v>
       </c>
       <c r="E376" t="str">
-        <v>0.132s</v>
+        <v>0.150s</v>
       </c>
     </row>
     <row r="377">
@@ -27268,7 +27268,7 @@
         <v>LOW</v>
       </c>
       <c r="E377" t="str">
-        <v>0.064s</v>
+        <v>0.082s</v>
       </c>
     </row>
     <row r="378">
@@ -27285,7 +27285,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E378" t="str">
-        <v>0.072s</v>
+        <v>0.120s</v>
       </c>
     </row>
     <row r="379">
@@ -27302,7 +27302,7 @@
         <v>LOW</v>
       </c>
       <c r="E379" t="str">
-        <v>0.157s</v>
+        <v>0.048s</v>
       </c>
     </row>
     <row r="380">
@@ -27319,7 +27319,7 @@
         <v>HIGH</v>
       </c>
       <c r="E380" t="str">
-        <v>0.160s</v>
+        <v>0.123s</v>
       </c>
     </row>
     <row r="381">
@@ -27336,7 +27336,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E381" t="str">
-        <v>0.128s</v>
+        <v>0.138s</v>
       </c>
     </row>
     <row r="382">
@@ -27353,7 +27353,7 @@
         <v>LOW</v>
       </c>
       <c r="E382" t="str">
-        <v>0.066s</v>
+        <v>0.111s</v>
       </c>
     </row>
     <row r="383">
@@ -27370,7 +27370,7 @@
         <v>HIGH</v>
       </c>
       <c r="E383" t="str">
-        <v>0.056s</v>
+        <v>0.148s</v>
       </c>
     </row>
     <row r="384">
@@ -27387,7 +27387,7 @@
         <v>LOW</v>
       </c>
       <c r="E384" t="str">
-        <v>0.116s</v>
+        <v>0.047s</v>
       </c>
     </row>
     <row r="385">
@@ -27404,7 +27404,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E385" t="str">
-        <v>0.155s</v>
+        <v>0.117s</v>
       </c>
     </row>
     <row r="386">
@@ -27421,7 +27421,7 @@
         <v>HIGH</v>
       </c>
       <c r="E386" t="str">
-        <v>0.073s</v>
+        <v>0.127s</v>
       </c>
     </row>
     <row r="387">
@@ -27438,7 +27438,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E387" t="str">
-        <v>0.125s</v>
+        <v>0.084s</v>
       </c>
     </row>
     <row r="388">
@@ -27455,7 +27455,7 @@
         <v>LOW</v>
       </c>
       <c r="E388" t="str">
-        <v>0.117s</v>
+        <v>0.131s</v>
       </c>
     </row>
     <row r="389">
@@ -27472,7 +27472,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E389" t="str">
-        <v>0.062s</v>
+        <v>0.150s</v>
       </c>
     </row>
     <row r="390">
@@ -27489,7 +27489,7 @@
         <v>LOW</v>
       </c>
       <c r="E390" t="str">
-        <v>0.079s</v>
+        <v>0.070s</v>
       </c>
     </row>
     <row r="391">
@@ -27506,7 +27506,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E391" t="str">
-        <v>0.160s</v>
+        <v>0.104s</v>
       </c>
     </row>
     <row r="392">
@@ -27523,7 +27523,7 @@
         <v>HIGH</v>
       </c>
       <c r="E392" t="str">
-        <v>0.075s</v>
+        <v>0.120s</v>
       </c>
     </row>
     <row r="393">
@@ -27540,7 +27540,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E393" t="str">
-        <v>0.143s</v>
+        <v>0.079s</v>
       </c>
     </row>
     <row r="394">
@@ -27557,7 +27557,7 @@
         <v>LOW</v>
       </c>
       <c r="E394" t="str">
-        <v>0.105s</v>
+        <v>0.133s</v>
       </c>
     </row>
     <row r="395">
@@ -27574,7 +27574,7 @@
         <v>HIGH</v>
       </c>
       <c r="E395" t="str">
-        <v>0.143s</v>
+        <v>0.113s</v>
       </c>
     </row>
     <row r="396">
@@ -27591,7 +27591,7 @@
         <v>LOW</v>
       </c>
       <c r="E396" t="str">
-        <v>0.050s</v>
+        <v>0.067s</v>
       </c>
     </row>
     <row r="397">
@@ -27608,7 +27608,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E397" t="str">
-        <v>0.138s</v>
+        <v>0.119s</v>
       </c>
     </row>
     <row r="398">
@@ -27625,7 +27625,7 @@
         <v>LOW</v>
       </c>
       <c r="E398" t="str">
-        <v>0.120s</v>
+        <v>0.097s</v>
       </c>
     </row>
     <row r="399">
@@ -27642,7 +27642,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E399" t="str">
-        <v>0.109s</v>
+        <v>0.054s</v>
       </c>
     </row>
     <row r="400">
@@ -27659,7 +27659,7 @@
         <v>HIGH</v>
       </c>
       <c r="E400" t="str">
-        <v>0.078s</v>
+        <v>0.061s</v>
       </c>
     </row>
     <row r="401">
@@ -27676,7 +27676,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E401" t="str">
-        <v>0.125s</v>
+        <v>0.109s</v>
       </c>
     </row>
     <row r="402">
@@ -27693,7 +27693,7 @@
         <v>LOW</v>
       </c>
       <c r="E402" t="str">
-        <v>0.096s</v>
+        <v>0.057s</v>
       </c>
     </row>
     <row r="403">
@@ -27710,7 +27710,7 @@
         <v>HIGH</v>
       </c>
       <c r="E403" t="str">
-        <v>0.060s</v>
+        <v>0.064s</v>
       </c>
     </row>
     <row r="404">
@@ -27727,7 +27727,7 @@
         <v>LOW</v>
       </c>
       <c r="E404" t="str">
-        <v>0.092s</v>
+        <v>0.112s</v>
       </c>
     </row>
     <row r="405">
@@ -27744,7 +27744,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E405" t="str">
-        <v>0.100s</v>
+        <v>0.118s</v>
       </c>
     </row>
     <row r="406">
@@ -27761,7 +27761,7 @@
         <v>HIGH</v>
       </c>
       <c r="E406" t="str">
-        <v>0.130s</v>
+        <v>0.104s</v>
       </c>
     </row>
     <row r="407">
@@ -27778,7 +27778,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E407" t="str">
-        <v>0.130s</v>
+        <v>0.110s</v>
       </c>
     </row>
     <row r="408">
@@ -27795,7 +27795,7 @@
         <v>LOW</v>
       </c>
       <c r="E408" t="str">
-        <v>0.107s</v>
+        <v>0.089s</v>
       </c>
     </row>
     <row r="409">
@@ -27812,7 +27812,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E409" t="str">
-        <v>0.045s</v>
+        <v>0.080s</v>
       </c>
     </row>
     <row r="410">
@@ -27829,7 +27829,7 @@
         <v>HIGH</v>
       </c>
       <c r="E410" t="str">
-        <v>0.047s</v>
+        <v>0.109s</v>
       </c>
     </row>
     <row r="411">
@@ -27846,7 +27846,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E411" t="str">
-        <v>0.130s</v>
+        <v>0.054s</v>
       </c>
     </row>
     <row r="412">
@@ -27863,7 +27863,7 @@
         <v>LOW</v>
       </c>
       <c r="E412" t="str">
-        <v>0.138s</v>
+        <v>0.142s</v>
       </c>
     </row>
     <row r="413">
@@ -27880,7 +27880,7 @@
         <v>HIGH</v>
       </c>
       <c r="E413" t="str">
-        <v>0.142s</v>
+        <v>0.056s</v>
       </c>
     </row>
     <row r="414">
@@ -27897,7 +27897,7 @@
         <v>LOW</v>
       </c>
       <c r="E414" t="str">
-        <v>0.091s</v>
+        <v>0.135s</v>
       </c>
     </row>
     <row r="415">
@@ -27914,7 +27914,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E415" t="str">
-        <v>0.131s</v>
+        <v>0.058s</v>
       </c>
     </row>
     <row r="416">
@@ -27931,7 +27931,7 @@
         <v>HIGH</v>
       </c>
       <c r="E416" t="str">
-        <v>0.143s</v>
+        <v>0.137s</v>
       </c>
     </row>
     <row r="417">
@@ -27948,7 +27948,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E417" t="str">
-        <v>0.043s</v>
+        <v>0.088s</v>
       </c>
     </row>
     <row r="418">
@@ -27965,7 +27965,7 @@
         <v>LOW</v>
       </c>
       <c r="E418" t="str">
-        <v>0.152s</v>
+        <v>0.119s</v>
       </c>
     </row>
     <row r="419">
@@ -27982,7 +27982,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E419" t="str">
-        <v>0.083s</v>
+        <v>0.127s</v>
       </c>
     </row>
     <row r="420">
@@ -27999,7 +27999,7 @@
         <v>LOW</v>
       </c>
       <c r="E420" t="str">
-        <v>0.084s</v>
+        <v>0.096s</v>
       </c>
     </row>
     <row r="421">
@@ -28016,7 +28016,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E421" t="str">
-        <v>0.071s</v>
+        <v>0.132s</v>
       </c>
     </row>
     <row r="422">
@@ -28033,7 +28033,7 @@
         <v>HIGH</v>
       </c>
       <c r="E422" t="str">
-        <v>0.125s</v>
+        <v>0.128s</v>
       </c>
     </row>
     <row r="423">
@@ -28050,7 +28050,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E423" t="str">
-        <v>0.105s</v>
+        <v>0.088s</v>
       </c>
     </row>
     <row r="424">
@@ -28067,7 +28067,7 @@
         <v>LOW</v>
       </c>
       <c r="E424" t="str">
-        <v>0.124s</v>
+        <v>0.079s</v>
       </c>
     </row>
     <row r="425">
@@ -28084,7 +28084,7 @@
         <v>HIGH</v>
       </c>
       <c r="E425" t="str">
-        <v>0.081s</v>
+        <v>0.078s</v>
       </c>
     </row>
     <row r="426">
@@ -28101,7 +28101,7 @@
         <v>LOW</v>
       </c>
       <c r="E426" t="str">
-        <v>0.136s</v>
+        <v>0.091s</v>
       </c>
     </row>
     <row r="427">
@@ -28118,7 +28118,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E427" t="str">
-        <v>0.059s</v>
+        <v>0.103s</v>
       </c>
     </row>
     <row r="428">
@@ -28135,7 +28135,7 @@
         <v>LOW</v>
       </c>
       <c r="E428" t="str">
-        <v>0.085s</v>
+        <v>0.127s</v>
       </c>
     </row>
     <row r="429">
@@ -28152,7 +28152,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E429" t="str">
-        <v>0.113s</v>
+        <v>0.044s</v>
       </c>
     </row>
     <row r="430">
@@ -28169,7 +28169,7 @@
         <v>HIGH</v>
       </c>
       <c r="E430" t="str">
-        <v>0.043s</v>
+        <v>0.126s</v>
       </c>
     </row>
     <row r="431">
@@ -28186,7 +28186,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E431" t="str">
-        <v>0.087s</v>
+        <v>0.053s</v>
       </c>
     </row>
     <row r="432">
@@ -28203,7 +28203,7 @@
         <v>LOW</v>
       </c>
       <c r="E432" t="str">
-        <v>0.059s</v>
+        <v>0.139s</v>
       </c>
     </row>
     <row r="433">
@@ -28220,7 +28220,7 @@
         <v>HIGH</v>
       </c>
       <c r="E433" t="str">
-        <v>0.062s</v>
+        <v>0.110s</v>
       </c>
     </row>
     <row r="434">
@@ -28237,7 +28237,7 @@
         <v>LOW</v>
       </c>
       <c r="E434" t="str">
-        <v>0.070s</v>
+        <v>0.054s</v>
       </c>
     </row>
     <row r="435">
@@ -28254,7 +28254,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E435" t="str">
-        <v>0.097s</v>
+        <v>0.068s</v>
       </c>
     </row>
     <row r="436">
@@ -28271,7 +28271,7 @@
         <v>HIGH</v>
       </c>
       <c r="E436" t="str">
-        <v>0.070s</v>
+        <v>0.082s</v>
       </c>
     </row>
     <row r="437">
@@ -28288,7 +28288,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E437" t="str">
-        <v>0.095s</v>
+        <v>0.060s</v>
       </c>
     </row>
     <row r="438">
@@ -28305,7 +28305,7 @@
         <v>LOW</v>
       </c>
       <c r="E438" t="str">
-        <v>0.145s</v>
+        <v>0.127s</v>
       </c>
     </row>
     <row r="439">
@@ -28322,7 +28322,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E439" t="str">
-        <v>0.130s</v>
+        <v>0.088s</v>
       </c>
     </row>
     <row r="440">
@@ -28339,7 +28339,7 @@
         <v>HIGH</v>
       </c>
       <c r="E440" t="str">
-        <v>0.154s</v>
+        <v>0.121s</v>
       </c>
     </row>
     <row r="441">
@@ -28356,7 +28356,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E441" t="str">
-        <v>0.074s</v>
+        <v>0.132s</v>
       </c>
     </row>
     <row r="442">
@@ -28373,7 +28373,7 @@
         <v>LOW</v>
       </c>
       <c r="E442" t="str">
-        <v>0.065s</v>
+        <v>0.128s</v>
       </c>
     </row>
     <row r="443">
@@ -28390,7 +28390,7 @@
         <v>HIGH</v>
       </c>
       <c r="E443" t="str">
-        <v>0.057s</v>
+        <v>0.116s</v>
       </c>
     </row>
     <row r="444">
@@ -28407,7 +28407,7 @@
         <v>LOW</v>
       </c>
       <c r="E444" t="str">
-        <v>0.093s</v>
+        <v>0.157s</v>
       </c>
     </row>
     <row r="445">
@@ -28424,7 +28424,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E445" t="str">
-        <v>0.154s</v>
+        <v>0.062s</v>
       </c>
     </row>
     <row r="446">
@@ -28458,7 +28458,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E447" t="str">
-        <v>0.157s</v>
+        <v>0.123s</v>
       </c>
     </row>
     <row r="448">
@@ -28475,7 +28475,7 @@
         <v>LOW</v>
       </c>
       <c r="E448" t="str">
-        <v>0.067s</v>
+        <v>0.100s</v>
       </c>
     </row>
     <row r="449">
@@ -28492,7 +28492,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E449" t="str">
-        <v>0.062s</v>
+        <v>0.128s</v>
       </c>
     </row>
     <row r="450">
@@ -28509,7 +28509,7 @@
         <v>LOW</v>
       </c>
       <c r="E450" t="str">
-        <v>0.159s</v>
+        <v>0.150s</v>
       </c>
     </row>
     <row r="451">
@@ -28526,7 +28526,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E451" t="str">
-        <v>0.151s</v>
+        <v>0.127s</v>
       </c>
     </row>
     <row r="452">
@@ -28543,7 +28543,7 @@
         <v>HIGH</v>
       </c>
       <c r="E452" t="str">
-        <v>0.138s</v>
+        <v>0.082s</v>
       </c>
     </row>
     <row r="453">
@@ -28560,7 +28560,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E453" t="str">
-        <v>0.087s</v>
+        <v>0.070s</v>
       </c>
     </row>
     <row r="454">
@@ -28577,7 +28577,7 @@
         <v>LOW</v>
       </c>
       <c r="E454" t="str">
-        <v>0.105s</v>
+        <v>0.148s</v>
       </c>
     </row>
     <row r="455">
@@ -28594,7 +28594,7 @@
         <v>HIGH</v>
       </c>
       <c r="E455" t="str">
-        <v>0.078s</v>
+        <v>0.096s</v>
       </c>
     </row>
     <row r="456">
@@ -28611,7 +28611,7 @@
         <v>LOW</v>
       </c>
       <c r="E456" t="str">
-        <v>0.096s</v>
+        <v>0.156s</v>
       </c>
     </row>
     <row r="457">
@@ -28628,7 +28628,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E457" t="str">
-        <v>0.107s</v>
+        <v>0.140s</v>
       </c>
     </row>
     <row r="458">
@@ -28645,7 +28645,7 @@
         <v>LOW</v>
       </c>
       <c r="E458" t="str">
-        <v>0.098s</v>
+        <v>0.153s</v>
       </c>
     </row>
     <row r="459">
@@ -28662,7 +28662,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E459" t="str">
-        <v>0.096s</v>
+        <v>0.151s</v>
       </c>
     </row>
     <row r="460">
@@ -28679,7 +28679,7 @@
         <v>HIGH</v>
       </c>
       <c r="E460" t="str">
-        <v>0.158s</v>
+        <v>0.124s</v>
       </c>
     </row>
     <row r="461">
@@ -28696,7 +28696,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E461" t="str">
-        <v>0.108s</v>
+        <v>0.137s</v>
       </c>
     </row>
     <row r="462">
@@ -28713,7 +28713,7 @@
         <v>LOW</v>
       </c>
       <c r="E462" t="str">
-        <v>0.091s</v>
+        <v>0.154s</v>
       </c>
     </row>
     <row r="463">
@@ -28730,7 +28730,7 @@
         <v>HIGH</v>
       </c>
       <c r="E463" t="str">
-        <v>0.081s</v>
+        <v>0.077s</v>
       </c>
     </row>
     <row r="464">
@@ -28747,7 +28747,7 @@
         <v>LOW</v>
       </c>
       <c r="E464" t="str">
-        <v>0.154s</v>
+        <v>0.115s</v>
       </c>
     </row>
     <row r="465">
@@ -28764,7 +28764,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E465" t="str">
-        <v>0.074s</v>
+        <v>0.103s</v>
       </c>
     </row>
     <row r="466">
@@ -28781,7 +28781,7 @@
         <v>HIGH</v>
       </c>
       <c r="E466" t="str">
-        <v>0.045s</v>
+        <v>0.087s</v>
       </c>
     </row>
     <row r="467">
@@ -28798,7 +28798,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E467" t="str">
-        <v>0.050s</v>
+        <v>0.141s</v>
       </c>
     </row>
     <row r="468">
@@ -28815,7 +28815,7 @@
         <v>LOW</v>
       </c>
       <c r="E468" t="str">
-        <v>0.061s</v>
+        <v>0.151s</v>
       </c>
     </row>
     <row r="469">
@@ -28832,7 +28832,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E469" t="str">
-        <v>0.067s</v>
+        <v>0.097s</v>
       </c>
     </row>
     <row r="470">
@@ -28849,7 +28849,7 @@
         <v>LOW</v>
       </c>
       <c r="E470" t="str">
-        <v>0.107s</v>
+        <v>0.064s</v>
       </c>
     </row>
     <row r="471">
@@ -28866,7 +28866,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E471" t="str">
-        <v>0.067s</v>
+        <v>0.148s</v>
       </c>
     </row>
     <row r="472">
@@ -28883,7 +28883,7 @@
         <v>HIGH</v>
       </c>
       <c r="E472" t="str">
-        <v>0.125s</v>
+        <v>0.072s</v>
       </c>
     </row>
     <row r="473">
@@ -28900,7 +28900,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E473" t="str">
-        <v>0.145s</v>
+        <v>0.107s</v>
       </c>
     </row>
     <row r="474">
@@ -28917,7 +28917,7 @@
         <v>LOW</v>
       </c>
       <c r="E474" t="str">
-        <v>0.147s</v>
+        <v>0.041s</v>
       </c>
     </row>
     <row r="475">
@@ -28934,7 +28934,7 @@
         <v>HIGH</v>
       </c>
       <c r="E475" t="str">
-        <v>0.062s</v>
+        <v>0.058s</v>
       </c>
     </row>
     <row r="476">
@@ -28951,7 +28951,7 @@
         <v>LOW</v>
       </c>
       <c r="E476" t="str">
-        <v>0.092s</v>
+        <v>0.064s</v>
       </c>
     </row>
     <row r="477">
@@ -28968,7 +28968,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E477" t="str">
-        <v>0.141s</v>
+        <v>0.081s</v>
       </c>
     </row>
     <row r="478">
@@ -28985,7 +28985,7 @@
         <v>HIGH</v>
       </c>
       <c r="E478" t="str">
-        <v>0.073s</v>
+        <v>0.147s</v>
       </c>
     </row>
     <row r="479">
@@ -29002,7 +29002,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E479" t="str">
-        <v>0.101s</v>
+        <v>0.140s</v>
       </c>
     </row>
     <row r="480">
@@ -29019,7 +29019,7 @@
         <v>LOW</v>
       </c>
       <c r="E480" t="str">
-        <v>0.081s</v>
+        <v>0.046s</v>
       </c>
     </row>
     <row r="481">
@@ -29036,7 +29036,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E481" t="str">
-        <v>0.063s</v>
+        <v>0.081s</v>
       </c>
     </row>
     <row r="482">
@@ -29053,7 +29053,7 @@
         <v>LOW</v>
       </c>
       <c r="E482" t="str">
-        <v>0.145s</v>
+        <v>0.103s</v>
       </c>
     </row>
     <row r="483">
@@ -29070,7 +29070,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E483" t="str">
-        <v>0.075s</v>
+        <v>0.073s</v>
       </c>
     </row>
     <row r="484">
@@ -29087,7 +29087,7 @@
         <v>HIGH</v>
       </c>
       <c r="E484" t="str">
-        <v>0.068s</v>
+        <v>0.094s</v>
       </c>
     </row>
     <row r="485">
@@ -29104,7 +29104,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E485" t="str">
-        <v>0.156s</v>
+        <v>0.047s</v>
       </c>
     </row>
     <row r="486">
@@ -29121,7 +29121,7 @@
         <v>LOW</v>
       </c>
       <c r="E486" t="str">
-        <v>0.156s</v>
+        <v>0.077s</v>
       </c>
     </row>
     <row r="487">
@@ -29138,7 +29138,7 @@
         <v>HIGH</v>
       </c>
       <c r="E487" t="str">
-        <v>0.090s</v>
+        <v>0.124s</v>
       </c>
     </row>
     <row r="488">
@@ -29155,7 +29155,7 @@
         <v>LOW</v>
       </c>
       <c r="E488" t="str">
-        <v>0.122s</v>
+        <v>0.044s</v>
       </c>
     </row>
     <row r="489">
@@ -29172,7 +29172,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E489" t="str">
-        <v>0.069s</v>
+        <v>0.155s</v>
       </c>
     </row>
     <row r="490">
@@ -29189,7 +29189,7 @@
         <v>HIGH</v>
       </c>
       <c r="E490" t="str">
-        <v>0.098s</v>
+        <v>0.076s</v>
       </c>
     </row>
     <row r="491">
@@ -29206,7 +29206,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E491" t="str">
-        <v>0.069s</v>
+        <v>0.091s</v>
       </c>
     </row>
     <row r="492">
@@ -29223,7 +29223,7 @@
         <v>LOW</v>
       </c>
       <c r="E492" t="str">
-        <v>0.050s</v>
+        <v>0.091s</v>
       </c>
     </row>
     <row r="493">
@@ -29240,7 +29240,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E493" t="str">
-        <v>0.056s</v>
+        <v>0.052s</v>
       </c>
     </row>
     <row r="494">
@@ -29257,7 +29257,7 @@
         <v>LOW</v>
       </c>
       <c r="E494" t="str">
-        <v>0.090s</v>
+        <v>0.133s</v>
       </c>
     </row>
     <row r="495">
@@ -29274,7 +29274,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E495" t="str">
-        <v>0.098s</v>
+        <v>0.074s</v>
       </c>
     </row>
     <row r="496">
@@ -29291,7 +29291,7 @@
         <v>HIGH</v>
       </c>
       <c r="E496" t="str">
-        <v>0.146s</v>
+        <v>0.117s</v>
       </c>
     </row>
     <row r="497">
@@ -29308,7 +29308,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E497" t="str">
-        <v>0.140s</v>
+        <v>0.083s</v>
       </c>
     </row>
     <row r="498">
@@ -29325,7 +29325,7 @@
         <v>LOW</v>
       </c>
       <c r="E498" t="str">
-        <v>0.081s</v>
+        <v>0.094s</v>
       </c>
     </row>
     <row r="499">
@@ -29342,7 +29342,7 @@
         <v>HIGH</v>
       </c>
       <c r="E499" t="str">
-        <v>0.102s</v>
+        <v>0.080s</v>
       </c>
     </row>
     <row r="500">
@@ -29359,7 +29359,7 @@
         <v>LOW</v>
       </c>
       <c r="E500" t="str">
-        <v>0.141s</v>
+        <v>0.125s</v>
       </c>
     </row>
     <row r="501">
@@ -29376,7 +29376,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E501" t="str">
-        <v>0.069s</v>
+        <v>0.095s</v>
       </c>
     </row>
     <row r="502">
@@ -29393,7 +29393,7 @@
         <v>HIGH</v>
       </c>
       <c r="E502" t="str">
-        <v>0.159s</v>
+        <v>0.141s</v>
       </c>
     </row>
     <row r="503">
@@ -29410,7 +29410,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E503" t="str">
-        <v>0.074s</v>
+        <v>0.141s</v>
       </c>
     </row>
     <row r="504">
@@ -29427,7 +29427,7 @@
         <v>LOW</v>
       </c>
       <c r="E504" t="str">
-        <v>0.125s</v>
+        <v>0.103s</v>
       </c>
     </row>
     <row r="505">
@@ -29444,7 +29444,7 @@
         <v>CRITICAL</v>
       </c>
       <c r="E505" t="str">
-        <v>0.041s</v>
+        <v>0.098s</v>
       </c>
     </row>
     <row r="506">
@@ -29461,7 +29461,7 @@
         <v>LOW</v>
       </c>
       <c r="E506" t="str">
-        <v>0.126s</v>
+        <v>0.053s</v>
       </c>
     </row>
     <row r="507">
@@ -29478,7 +29478,7 @@
         <v>MEDIUM</v>
       </c>
       <c r="E507" t="str">
-        <v>0.139s</v>
+        <v>0.138s</v>
       </c>
     </row>
   </sheetData>
@@ -29703,7 +29703,7 @@
         <v>Execution Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>0.33s</v>
+        <v>0.31s</v>
       </c>
     </row>
     <row r="11">
